--- a/Produccion Astroflores BL25-26-27-28 a la Semana 21_entrenamiento.xlsx
+++ b/Produccion Astroflores BL25-26-27-28 a la Semana 21_entrenamiento.xlsx
@@ -4,19 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="20115" windowHeight="7755"/>
+    <workbookView xWindow="9195" yWindow="-30" windowWidth="13815" windowHeight="7815"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$K$609</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="26">
   <si>
     <t>Anio</t>
   </si>
@@ -471,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K617"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -21854,7 +21857,7 @@
         <v>12800</v>
       </c>
       <c r="K578" s="6">
-        <f t="shared" ref="K578:K609" si="18">+H578/I578</f>
+        <f t="shared" ref="K578:K617" si="18">+H578/I578</f>
         <v>0.43864646234476468</v>
       </c>
     </row>
@@ -21878,7 +21881,7 @@
         <v>17</v>
       </c>
       <c r="G579" s="4" t="str">
-        <f t="shared" ref="G579:G609" si="19">+E579&amp;F579</f>
+        <f t="shared" ref="G579:G617" si="19">+E579&amp;F579</f>
         <v>025PINK MONDIAL</v>
       </c>
       <c r="H579" s="4">
@@ -23005,7 +23008,308 @@
         <v>0.82032585165774174</v>
       </c>
     </row>
+    <row r="610" spans="1:11">
+      <c r="A610" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B610" s="4">
+        <v>26</v>
+      </c>
+      <c r="C610" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D610" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E610" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F610" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G610" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>026PURPLE BUBBLY</v>
+      </c>
+      <c r="H610" s="4">
+        <v>740</v>
+      </c>
+      <c r="I610" s="4">
+        <v>1755.4</v>
+      </c>
+      <c r="J610" s="4">
+        <v>12800</v>
+      </c>
+      <c r="K610" s="6">
+        <f t="shared" si="18"/>
+        <v>0.42155634043522844</v>
+      </c>
+    </row>
+    <row r="611" spans="1:11">
+      <c r="A611" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B611" s="4">
+        <v>26</v>
+      </c>
+      <c r="C611" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D611" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E611" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F611" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G611" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>025PINK MONDIAL</v>
+      </c>
+      <c r="H611" s="4">
+        <v>4425</v>
+      </c>
+      <c r="I611" s="4">
+        <v>3071.9505625000002</v>
+      </c>
+      <c r="J611" s="4">
+        <v>22400</v>
+      </c>
+      <c r="K611" s="6">
+        <f t="shared" si="18"/>
+        <v>1.4404528686161107</v>
+      </c>
+    </row>
+    <row r="612" spans="1:11">
+      <c r="A612" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B612" s="4">
+        <v>26</v>
+      </c>
+      <c r="C612" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D612" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E612" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F612" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G612" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>026LOLA</v>
+      </c>
+      <c r="H612" s="4">
+        <v>4325</v>
+      </c>
+      <c r="I612" s="4">
+        <v>1097.125</v>
+      </c>
+      <c r="J612" s="4">
+        <v>8000</v>
+      </c>
+      <c r="K612" s="6">
+        <f t="shared" si="18"/>
+        <v>3.9421214537997038</v>
+      </c>
+    </row>
+    <row r="613" spans="1:11">
+      <c r="A613" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B613" s="4">
+        <v>26</v>
+      </c>
+      <c r="C613" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D613" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E613" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F613" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G613" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>026PALOMA</v>
+      </c>
+      <c r="H613" s="4">
+        <v>4800</v>
+      </c>
+      <c r="I613" s="4">
+        <v>2852.5250000000001</v>
+      </c>
+      <c r="J613" s="4">
+        <v>20800</v>
+      </c>
+      <c r="K613" s="6">
+        <f t="shared" si="18"/>
+        <v>1.6827196957081882</v>
+      </c>
+    </row>
+    <row r="614" spans="1:11">
+      <c r="A614" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B614" s="4">
+        <v>26</v>
+      </c>
+      <c r="C614" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D614" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E614" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F614" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G614" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>027SATISFACTION</v>
+      </c>
+      <c r="H614" s="4">
+        <v>2250</v>
+      </c>
+      <c r="I614" s="4">
+        <v>2633.1</v>
+      </c>
+      <c r="J614" s="4">
+        <v>19200</v>
+      </c>
+      <c r="K614" s="6">
+        <f t="shared" si="18"/>
+        <v>0.85450609547681444</v>
+      </c>
+    </row>
+    <row r="615" spans="1:11">
+      <c r="A615" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B615" s="4">
+        <v>26</v>
+      </c>
+      <c r="C615" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D615" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E615" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F615" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G615" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>027TIFFANY!</v>
+      </c>
+      <c r="H615" s="4">
+        <v>2700</v>
+      </c>
+      <c r="I615" s="4">
+        <v>2633.1</v>
+      </c>
+      <c r="J615" s="4">
+        <v>19200</v>
+      </c>
+      <c r="K615" s="6">
+        <f t="shared" si="18"/>
+        <v>1.0254073145721774</v>
+      </c>
+    </row>
+    <row r="616" spans="1:11">
+      <c r="A616" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B616" s="4">
+        <v>26</v>
+      </c>
+      <c r="C616" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D616" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E616" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F616" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G616" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>028COTOPAXI</v>
+      </c>
+      <c r="H616" s="4">
+        <v>2670</v>
+      </c>
+      <c r="I616" s="4">
+        <v>2852.5250000000001</v>
+      </c>
+      <c r="J616" s="4">
+        <v>20800</v>
+      </c>
+      <c r="K616" s="6">
+        <f t="shared" si="18"/>
+        <v>0.93601283073767971</v>
+      </c>
+    </row>
+    <row r="617" spans="1:11">
+      <c r="A617" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B617" s="4">
+        <v>26</v>
+      </c>
+      <c r="C617" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D617" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E617" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F617" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G617" s="4" t="str">
+        <f t="shared" si="19"/>
+        <v>028DEEP PURPLE</v>
+      </c>
+      <c r="H617" s="4">
+        <v>3420</v>
+      </c>
+      <c r="I617" s="4">
+        <v>2852.5250000000001</v>
+      </c>
+      <c r="J617" s="4">
+        <v>20800</v>
+      </c>
+      <c r="K617" s="6">
+        <f t="shared" si="18"/>
+        <v>1.1989377831920842</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:K609">
+    <filterColumn colId="0"/>
+    <filterColumn colId="1"/>
+    <filterColumn colId="5"/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Produccion Astroflores BL25-26-27-28 a la Semana 21_entrenamiento.xlsx
+++ b/Produccion Astroflores BL25-26-27-28 a la Semana 21_entrenamiento.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$K$609</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$K$617</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="27">
   <si>
     <t>Anio</t>
   </si>
@@ -98,6 +98,9 @@
   <si>
     <t>DEEP PURPLE</t>
   </si>
+  <si>
+    <t>Estimado</t>
+  </si>
 </sst>
 </file>
 
@@ -140,7 +143,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -163,12 +166,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -179,6 +202,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -474,10 +500,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K617"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L617"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,8 +542,11 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" hidden="1">
       <c r="A2" s="3">
         <v>2025</v>
       </c>
@@ -549,7 +583,7 @@
         <v>0.84311268087045688</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12" hidden="1">
       <c r="A3" s="3">
         <v>2025</v>
       </c>
@@ -586,7 +620,7 @@
         <v>1.4892817794166568</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12" hidden="1">
       <c r="A4" s="3">
         <v>2025</v>
       </c>
@@ -623,7 +657,7 @@
         <v>2.6250427253047737</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12" hidden="1">
       <c r="A5" s="3">
         <v>2025</v>
       </c>
@@ -660,7 +694,7 @@
         <v>1.4723797337446647</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12" hidden="1">
       <c r="A6" s="3">
         <v>2025</v>
       </c>
@@ -697,7 +731,7 @@
         <v>1.3786031673692607</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12" hidden="1">
       <c r="A7" s="3">
         <v>2025</v>
       </c>
@@ -734,7 +768,7 @@
         <v>1.4811438988264785</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12" hidden="1">
       <c r="A8" s="3">
         <v>2025</v>
       </c>
@@ -771,7 +805,7 @@
         <v>1.8825426595735357</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12" hidden="1">
       <c r="A9" s="3">
         <v>2025</v>
       </c>
@@ -808,7 +842,7 @@
         <v>1.724787688100893</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12" hidden="1">
       <c r="A10" s="3">
         <v>2025</v>
       </c>
@@ -845,7 +879,7 @@
         <v>0.90007975390224448</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12" hidden="1">
       <c r="A11" s="3">
         <v>2025</v>
       </c>
@@ -882,7 +916,7 @@
         <v>1.521834386617021</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12" hidden="1">
       <c r="A12" s="3">
         <v>2025</v>
       </c>
@@ -919,7 +953,7 @@
         <v>4.2110060385097414</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12" hidden="1">
       <c r="A13" s="3">
         <v>2025</v>
       </c>
@@ -956,7 +990,7 @@
         <v>1.7528330163626962</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12" hidden="1">
       <c r="A14" s="3">
         <v>2025</v>
       </c>
@@ -993,7 +1027,7 @@
         <v>1.2304887774866127</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:12" hidden="1">
       <c r="A15" s="3">
         <v>2025</v>
       </c>
@@ -1030,7 +1064,7 @@
         <v>1.3444229235501881</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:12" hidden="1">
       <c r="A16" s="3">
         <v>2025</v>
       </c>
@@ -1067,7 +1101,7 @@
         <v>1.4723797337446647</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="3">
         <v>2025</v>
       </c>
@@ -1104,7 +1138,7 @@
         <v>1.840474667180831</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" hidden="1">
       <c r="A18" s="3">
         <v>2025</v>
       </c>
@@ -1141,7 +1175,7 @@
         <v>1.2817591432152216</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" s="3">
         <v>2025</v>
       </c>
@@ -1178,7 +1212,7 @@
         <v>2.1240576198237564</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" hidden="1">
       <c r="A20" s="3">
         <v>2025</v>
       </c>
@@ -1215,7 +1249,7 @@
         <v>6.6719835934829668</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" hidden="1">
       <c r="A21" s="3">
         <v>2025</v>
       </c>
@@ -1252,7 +1286,7 @@
         <v>1.8159350049517533</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" s="3">
         <v>2025</v>
       </c>
@@ -1289,7 +1323,7 @@
         <v>2.1533553606015725</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" hidden="1">
       <c r="A23" s="3">
         <v>2025</v>
       </c>
@@ -1326,7 +1360,7 @@
         <v>2.2672895066651475</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" hidden="1">
       <c r="A24" s="3">
         <v>2025</v>
       </c>
@@ -1363,7 +1397,7 @@
         <v>1.5670327166282503</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" hidden="1">
       <c r="A25" s="3">
         <v>2025</v>
       </c>
@@ -1400,7 +1434,7 @@
         <v>3.2918204047291435</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" s="3">
         <v>2025</v>
       </c>
@@ -1437,7 +1471,7 @@
         <v>1.8742167027458128</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" hidden="1">
       <c r="A27" s="3">
         <v>2025</v>
       </c>
@@ -1474,7 +1508,7 @@
         <v>2.7262808530304921</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" hidden="1">
       <c r="A28" s="3">
         <v>2025</v>
       </c>
@@ -1511,7 +1545,7 @@
         <v>10.263187877406859</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" hidden="1">
       <c r="A29" s="3">
         <v>2025</v>
       </c>
@@ -1548,7 +1582,7 @@
         <v>3.9263459566524395</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" hidden="1">
       <c r="A30" s="3">
         <v>2025</v>
       </c>
@@ -1585,7 +1619,7 @@
         <v>4.3181041358095023</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" hidden="1">
       <c r="A31" s="3">
         <v>2025</v>
       </c>
@@ -1622,7 +1656,7 @@
         <v>3.6344992594280505</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" hidden="1">
       <c r="A32" s="3">
         <v>2025</v>
       </c>
@@ -1659,7 +1693,7 @@
         <v>3.3338883971218483</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" hidden="1">
       <c r="A33" s="3">
         <v>2025</v>
       </c>
@@ -1696,7 +1730,7 @@
         <v>6.562606813261934</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" hidden="1">
       <c r="A34" s="3">
         <v>2025</v>
       </c>
@@ -1733,7 +1767,7 @@
         <v>1.5324142645550871</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" hidden="1">
       <c r="A35" s="3">
         <v>2025</v>
       </c>
@@ -1770,7 +1804,7 @@
         <v>3.9063128640436902</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" hidden="1">
       <c r="A36" s="3">
         <v>2025</v>
       </c>
@@ -1807,7 +1841,7 @@
         <v>7.2735558846986441</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" hidden="1">
       <c r="A37" s="3">
         <v>2025</v>
       </c>
@@ -1844,7 +1878,7 @@
         <v>3.8912892963251853</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" hidden="1">
       <c r="A38" s="3">
         <v>2025</v>
       </c>
@@ -1881,7 +1915,7 @@
         <v>6.2435912042839243</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" hidden="1">
       <c r="A39" s="3">
         <v>2025</v>
       </c>
@@ -1918,7 +1952,7 @@
         <v>5.5941665717215452</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" hidden="1">
       <c r="A40" s="3">
         <v>2025</v>
       </c>
@@ -1955,7 +1989,7 @@
         <v>3.4075073838090812</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" hidden="1">
       <c r="A41" s="3">
         <v>2025</v>
       </c>
@@ -1992,7 +2026,7 @@
         <v>8.7816934119771073</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" hidden="1">
       <c r="A42" s="3">
         <v>2025</v>
       </c>
@@ -2029,7 +2063,7 @@
         <v>0.50700694998290985</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" hidden="1">
       <c r="A43" s="3">
         <v>2025</v>
       </c>
@@ -2066,7 +2100,7 @@
         <v>2.734419004830583</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" hidden="1">
       <c r="A44" s="3">
         <v>2025</v>
       </c>
@@ -2103,7 +2137,7 @@
         <v>3.6458926740344082</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" hidden="1">
       <c r="A45" s="3">
         <v>2025</v>
       </c>
@@ -2140,7 +2174,7 @@
         <v>2.1735129402897431</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" hidden="1">
       <c r="A46" s="3">
         <v>2025</v>
       </c>
@@ -2177,7 +2211,7 @@
         <v>3.3610573088754703</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" hidden="1">
       <c r="A47" s="3">
         <v>2025</v>
       </c>
@@ -2214,7 +2248,7 @@
         <v>3.1331890167483194</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" hidden="1">
       <c r="A48" s="3">
         <v>2025</v>
       </c>
@@ -2251,7 +2285,7 @@
         <v>2.566147535954987</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" hidden="1">
       <c r="A49" s="3">
         <v>2025</v>
       </c>
@@ -2288,7 +2322,7 @@
         <v>4.7536831403756317</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" hidden="1">
       <c r="A50" s="3">
         <v>2025</v>
       </c>
@@ -2325,7 +2359,7 @@
         <v>0.55827731571151873</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" hidden="1">
       <c r="A51" s="3">
         <v>2025</v>
       </c>
@@ -2362,7 +2396,7 @@
         <v>1.9124656730213898</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" hidden="1">
       <c r="A52" s="3">
         <v>2025</v>
       </c>
@@ -2399,7 +2433,7 @@
         <v>3.4089096502221716</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" hidden="1">
       <c r="A53" s="3">
         <v>2025</v>
       </c>
@@ -2436,7 +2470,7 @@
         <v>2.1665016082242925</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" hidden="1">
       <c r="A54" s="3">
         <v>2025</v>
       </c>
@@ -2473,7 +2507,7 @@
         <v>2.0849948729634273</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" hidden="1">
       <c r="A55" s="3">
         <v>2025</v>
       </c>
@@ -2510,7 +2544,7 @@
         <v>2.0508146291443548</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" hidden="1">
       <c r="A56" s="3">
         <v>2025</v>
       </c>
@@ -2547,7 +2581,7 @@
         <v>1.367209752762903</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" hidden="1">
       <c r="A57" s="3">
         <v>2025</v>
       </c>
@@ -2584,7 +2618,7 @@
         <v>3.1340654332565006</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" hidden="1">
       <c r="A58" s="3">
         <v>2025</v>
       </c>
@@ -2621,7 +2655,7 @@
         <v>0.25065512133986556</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" hidden="1">
       <c r="A59" s="3">
         <v>2025</v>
       </c>
@@ -2658,7 +2692,7 @@
         <v>1.0905123412121969</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="3">
         <v>2025</v>
       </c>
@@ -2695,7 +2729,7 @@
         <v>1.9870115073487524</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" hidden="1">
       <c r="A61" s="3">
         <v>2025</v>
       </c>
@@ -2732,7 +2766,7 @@
         <v>1.4934137299410171</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" hidden="1">
       <c r="A62" s="3">
         <v>2025</v>
       </c>
@@ -2769,7 +2803,7 @@
         <v>1.2874558505184004</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="3">
         <v>2025</v>
       </c>
@@ -2806,7 +2840,7 @@
         <v>1.4127834111883333</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" hidden="1">
       <c r="A64" s="3">
         <v>2025</v>
       </c>
@@ -2843,7 +2877,7 @@
         <v>0.99911481932673685</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" hidden="1">
       <c r="A65" s="3">
         <v>2025</v>
       </c>
@@ -2880,7 +2914,7 @@
         <v>1.7353046861990691</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" hidden="1">
       <c r="A66" s="3">
         <v>2025</v>
       </c>
@@ -2917,7 +2951,7 @@
         <v>0.27913865785575936</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" hidden="1">
       <c r="A67" s="3">
         <v>2025</v>
       </c>
@@ -2954,7 +2988,7 @@
         <v>1.1556175556129249</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" s="3">
         <v>2025</v>
       </c>
@@ -2991,7 +3025,7 @@
         <v>2.9349436025976985</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" s="3">
         <v>2025</v>
       </c>
@@ -3028,7 +3062,7 @@
         <v>1.689731027773639</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" s="3">
         <v>2025</v>
       </c>
@@ -3065,7 +3099,7 @@
         <v>1.2760624359120429</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="3">
         <v>2025</v>
       </c>
@@ -3102,7 +3136,7 @@
         <v>1.4241768257946907</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="3">
         <v>2025</v>
       </c>
@@ -3139,7 +3173,7 @@
         <v>1.7984066747881262</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="3">
         <v>2025</v>
       </c>
@@ -3176,7 +3210,7 @@
         <v>1.6196177071191313</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="3">
         <v>2025</v>
       </c>
@@ -3213,7 +3247,7 @@
         <v>0.23356499943032927</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="3">
         <v>2025</v>
       </c>
@@ -3250,7 +3284,7 @@
         <v>1.2044464664134711</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="3">
         <v>2025</v>
       </c>
@@ -3287,7 +3321,7 @@
         <v>2.1146177509399569</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" hidden="1">
       <c r="A77" s="3">
         <v>2025</v>
       </c>
@@ -3324,7 +3358,7 @@
         <v>1.2830737679774935</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" hidden="1">
       <c r="A78" s="3">
         <v>2025</v>
       </c>
@@ -3361,7 +3395,7 @@
         <v>1.3558163381565456</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" hidden="1">
       <c r="A79" s="3">
         <v>2025</v>
       </c>
@@ -3398,7 +3432,7 @@
         <v>1.4583570696137633</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" hidden="1">
       <c r="A80" s="3">
         <v>2025</v>
       </c>
@@ -3435,7 +3469,7 @@
         <v>1.7458216842972454</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" hidden="1">
       <c r="A81" s="3">
         <v>2025</v>
       </c>
@@ -3472,7 +3506,7 @@
         <v>1.3461757565665506</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" hidden="1">
       <c r="A82" s="3">
         <v>2025</v>
       </c>
@@ -3509,7 +3543,7 @@
         <v>0.23926170673350802</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="3">
         <v>2025</v>
       </c>
@@ -3546,7 +3580,7 @@
         <v>1.6764592708187502</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="3">
         <v>2025</v>
       </c>
@@ -3583,7 +3617,7 @@
         <v>2.5703543351942577</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" s="3">
         <v>2025</v>
       </c>
@@ -3620,7 +3654,7 @@
         <v>1.4793910658101155</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" s="3">
         <v>2025</v>
       </c>
@@ -3657,7 +3691,7 @@
         <v>1.3330295089438304</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" s="3">
         <v>2025</v>
       </c>
@@ -3694,7 +3728,7 @@
         <v>1.5039307280391934</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" hidden="1">
       <c r="A88" s="3">
         <v>2025</v>
       </c>
@@ -3731,7 +3765,7 @@
         <v>1.5565157185300742</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" hidden="1">
       <c r="A89" s="3">
         <v>2025</v>
       </c>
@@ -3768,7 +3802,7 @@
         <v>1.2935907660756698</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" hidden="1">
       <c r="A90" s="3">
         <v>2025</v>
       </c>
@@ -3805,7 +3839,7 @@
         <v>0.30762219437165317</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" hidden="1">
       <c r="A91" s="3">
         <v>2025</v>
       </c>
@@ -3842,7 +3876,7 @@
         <v>1.546248842017294</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" hidden="1">
       <c r="A92" s="3">
         <v>2025</v>
       </c>
@@ -3879,7 +3913,7 @@
         <v>2.8984846758573544</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" hidden="1">
       <c r="A93" s="3">
         <v>2025</v>
       </c>
@@ -3916,7 +3950,7 @@
         <v>1.528470390268271</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" hidden="1">
       <c r="A94" s="3">
         <v>2025</v>
       </c>
@@ -3953,7 +3987,7 @@
         <v>1.15073487524211</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" hidden="1">
       <c r="A95" s="3">
         <v>2025</v>
       </c>
@@ -3990,7 +4024,7 @@
         <v>1.3330295089438304</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" hidden="1">
       <c r="A96" s="3">
         <v>2025</v>
       </c>
@@ -4027,7 +4061,7 @@
         <v>2.0613316272425308</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" hidden="1">
       <c r="A97" s="3">
         <v>2025</v>
       </c>
@@ -4064,7 +4098,7 @@
         <v>1.0411828117194415</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" hidden="1">
       <c r="A98" s="3">
         <v>2025</v>
       </c>
@@ -4101,7 +4135,7 @@
         <v>0.31901560897801068</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" hidden="1">
       <c r="A99" s="3">
         <v>2025</v>
       </c>
@@ -4138,7 +4172,7 @@
         <v>1.5543869938173849</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" hidden="1">
       <c r="A100" s="3">
         <v>2025</v>
       </c>
@@ -4175,7 +4209,7 @@
         <v>2.9531730659678708</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" hidden="1">
       <c r="A101" s="3">
         <v>2025</v>
       </c>
@@ -4212,7 +4246,7 @@
         <v>1.4303117413519602</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" hidden="1">
       <c r="A102" s="3">
         <v>2025</v>
       </c>
@@ -4249,7 +4283,7 @@
         <v>1.2304887774866127</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" hidden="1">
       <c r="A103" s="3">
         <v>2025</v>
       </c>
@@ -4286,7 +4320,7 @@
         <v>1.4127834111883333</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" hidden="1">
       <c r="A104" s="3">
         <v>2025</v>
       </c>
@@ -4323,7 +4357,7 @@
         <v>2.2401205949115255</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" hidden="1">
       <c r="A105" s="3">
         <v>2025</v>
       </c>
@@ -4360,7 +4394,7 @@
         <v>1.0306658136212654</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" hidden="1">
       <c r="A106" s="3">
         <v>2025</v>
       </c>
@@ -4397,7 +4431,7 @@
         <v>0.27344195055258058</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" hidden="1">
       <c r="A107" s="3">
         <v>2025</v>
       </c>
@@ -4434,7 +4468,7 @@
         <v>1.2451372254139261</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" hidden="1">
       <c r="A108" s="3">
         <v>2025</v>
       </c>
@@ -4471,7 +4505,7 @@
         <v>2.8620257491170102</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" hidden="1">
       <c r="A109" s="3">
         <v>2025</v>
       </c>
@@ -4508,7 +4542,7 @@
         <v>1.0657224739485192</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" hidden="1">
       <c r="A110" s="3">
         <v>2025</v>
       </c>
@@ -4545,7 +4579,7 @@
         <v>1.3899965819756182</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" hidden="1">
       <c r="A111" s="3">
         <v>2025</v>
       </c>
@@ -4582,7 +4616,7 @@
         <v>1.4811438988264785</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" hidden="1">
       <c r="A112" s="3">
         <v>2025</v>
       </c>
@@ -4619,7 +4653,7 @@
         <v>1.8089236728863025</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" hidden="1">
       <c r="A113" s="3">
         <v>2025</v>
       </c>
@@ -4656,7 +4690,7 @@
         <v>0.98859782122856066</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" hidden="1">
       <c r="A114" s="3">
         <v>2025</v>
       </c>
@@ -4693,7 +4727,7 @@
         <v>0.29053207246211687</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" hidden="1">
       <c r="A115" s="3">
         <v>2025</v>
       </c>
@@ -4730,7 +4764,7 @@
         <v>1.1800320110131981</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" hidden="1">
       <c r="A116" s="3">
         <v>2025</v>
       </c>
@@ -4767,7 +4801,7 @@
         <v>4.0469408681781927</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" hidden="1">
       <c r="A117" s="3">
         <v>2025</v>
       </c>
@@ -4804,7 +4838,7 @@
         <v>1.5144477261373694</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" hidden="1">
       <c r="A118" s="3">
         <v>2025</v>
       </c>
@@ -4841,7 +4875,7 @@
         <v>1.15073487524211</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" hidden="1">
       <c r="A119" s="3">
         <v>2025</v>
       </c>
@@ -4878,7 +4912,7 @@
         <v>1.2190953628802552</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" hidden="1">
       <c r="A120" s="3">
         <v>2025</v>
       </c>
@@ -4915,7 +4949,7 @@
         <v>1.8825426595735357</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" s="3">
         <v>2025</v>
       </c>
@@ -4952,7 +4986,7 @@
         <v>1.7458216842972454</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" hidden="1">
       <c r="A122" s="3">
         <v>2025</v>
       </c>
@@ -4989,7 +5023,7 @@
         <v>0.56967073031787618</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" hidden="1">
       <c r="A123" s="3">
         <v>2025</v>
       </c>
@@ -5026,7 +5060,7 @@
         <v>1.7171500298192053</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" hidden="1">
       <c r="A124" s="3">
         <v>2025</v>
       </c>
@@ -5063,7 +5097,7 @@
         <v>8.3126352967984509</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" hidden="1">
       <c r="A125" s="3">
         <v>2025</v>
       </c>
@@ -5100,7 +5134,7 @@
         <v>2.41189823051507</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" hidden="1">
       <c r="A126" s="3">
         <v>2025</v>
       </c>
@@ -5137,7 +5171,7 @@
         <v>1.7431924347727015</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" hidden="1">
       <c r="A127" s="3">
         <v>2025</v>
       </c>
@@ -5174,7 +5208,7 @@
         <v>1.7204056055599863</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" hidden="1">
       <c r="A128" s="3">
         <v>2025</v>
       </c>
@@ -5211,7 +5245,7 @@
         <v>1.6827196957081882</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" hidden="1">
       <c r="A129" s="3">
         <v>2025</v>
       </c>
@@ -5248,7 +5282,7 @@
         <v>3.7861193153434236</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" hidden="1">
       <c r="A130" s="3">
         <v>2025</v>
       </c>
@@ -5285,7 +5319,7 @@
         <v>0.8658995100831719</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" hidden="1">
       <c r="A131" s="3">
         <v>2025</v>
       </c>
@@ -5322,7 +5356,7 @@
         <v>3.4587145150386838</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" hidden="1">
       <c r="A132" s="3">
         <v>2025</v>
       </c>
@@ -5359,7 +5393,7 @@
         <v>8.5496183206106871</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" hidden="1">
       <c r="A133" s="3">
         <v>2025</v>
       </c>
@@ -5396,7 +5430,7 @@
         <v>3.8772666321942837</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" hidden="1">
       <c r="A134" s="3">
         <v>2025</v>
       </c>
@@ -5433,7 +5467,7 @@
         <v>3.6117124302153356</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" hidden="1">
       <c r="A135" s="3">
         <v>2025</v>
       </c>
@@ -5470,7 +5504,7 @@
         <v>3.4863848695454029</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" hidden="1">
       <c r="A136" s="3">
         <v>2025</v>
       </c>
@@ -5507,7 +5541,7 @@
         <v>1.2830737679774935</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" hidden="1">
       <c r="A137" s="3">
         <v>2025</v>
       </c>
@@ -5544,7 +5578,7 @@
         <v>7.5406876363923185</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" hidden="1">
       <c r="A138" s="3">
         <v>2025</v>
       </c>
@@ -5581,7 +5615,7 @@
         <v>0.91716987581178078</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" hidden="1">
       <c r="A139" s="3">
         <v>2025</v>
       </c>
@@ -5618,7 +5652,7 @@
         <v>2.9785635588333137</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" hidden="1">
       <c r="A140" s="3">
         <v>2025</v>
       </c>
@@ -5655,7 +5689,7 @@
         <v>6.5990657400022785</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" hidden="1">
       <c r="A141" s="3">
         <v>2025</v>
       </c>
@@ -5692,7 +5726,7 @@
         <v>3.4916433685944908</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" hidden="1">
       <c r="A142" s="3">
         <v>2025</v>
       </c>
@@ -5729,7 +5763,7 @@
         <v>4.8080209638828757</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" hidden="1">
       <c r="A143" s="3">
         <v>2025</v>
       </c>
@@ -5766,7 +5800,7 @@
         <v>4.5687592571493676</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" hidden="1">
       <c r="A144" s="3">
         <v>2025</v>
       </c>
@@ -5803,7 +5837,7 @@
         <v>2.6292495245440444</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" hidden="1">
       <c r="A145" s="3">
         <v>2025</v>
       </c>
@@ -5840,7 +5874,7 @@
         <v>6.6151918037528157</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" hidden="1">
       <c r="A146" s="3">
         <v>2025</v>
       </c>
@@ -5877,7 +5911,7 @@
         <v>0.38167938931297707</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147" s="3">
         <v>2025</v>
       </c>
@@ -5914,7 +5948,7 @@
         <v>1.8880512176211168</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" hidden="1">
       <c r="A148" s="3">
         <v>2025</v>
       </c>
@@ -5951,7 +5985,7 @@
         <v>3.4271391135923435</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="3">
         <v>2025</v>
       </c>
@@ -5988,7 +6022,7 @@
         <v>1.8580029973444578</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" hidden="1">
       <c r="A150" s="3">
         <v>2025</v>
       </c>
@@ -6025,7 +6059,7 @@
         <v>2.0736014583570697</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" hidden="1">
       <c r="A151" s="3">
         <v>2025</v>
       </c>
@@ -6062,7 +6096,7 @@
         <v>2.1647487752079297</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152" s="3">
         <v>2025</v>
       </c>
@@ -6099,7 +6133,7 @@
         <v>3.3444053952200243</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153" s="3">
         <v>2025</v>
       </c>
@@ -6136,7 +6170,7 @@
         <v>4.0280102716014756</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154" s="3">
         <v>2025</v>
       </c>
@@ -6173,7 +6207,7 @@
         <v>0.47852341346701605</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" hidden="1">
       <c r="A155" s="3">
         <v>2025</v>
       </c>
@@ -6210,7 +6244,7 @@
         <v>2.4658599954275795</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156" s="3">
         <v>2025</v>
       </c>
@@ -6247,7 +6281,7 @@
         <v>3.9011051612168166</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" hidden="1">
       <c r="A157" s="3">
         <v>2025</v>
       </c>
@@ -6284,7 +6318,7 @@
         <v>2.3838529022532668</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" hidden="1">
       <c r="A158" s="3">
         <v>2025</v>
       </c>
@@ -6321,7 +6355,7 @@
         <v>2.1989290190270023</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" hidden="1">
       <c r="A159" s="3">
         <v>2025</v>
       </c>
@@ -6358,7 +6392,7 @@
         <v>2.0963882875697846</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" hidden="1">
       <c r="A160" s="3">
         <v>2025</v>
       </c>
@@ -6395,7 +6429,7 @@
         <v>3.1550994294528532</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" hidden="1">
       <c r="A161" s="3">
         <v>2025</v>
       </c>
@@ -6432,7 +6466,7 @@
         <v>4.1016292582887086</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" hidden="1">
       <c r="A162" s="3">
         <v>2025</v>
       </c>
@@ -6469,7 +6503,7 @@
         <v>0.34180243819072575</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" hidden="1">
       <c r="A163" s="3">
         <v>2025</v>
       </c>
@@ -6506,7 +6540,7 @@
         <v>1.4160384132158377</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" hidden="1">
       <c r="A164" s="3">
         <v>2025</v>
       </c>
@@ -6543,7 +6577,7 @@
         <v>3.1172382362994191</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" hidden="1">
       <c r="A165" s="3">
         <v>2025</v>
       </c>
@@ -6580,7 +6614,7 @@
         <v>1.7317990201663438</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" hidden="1">
       <c r="A166" s="3">
         <v>2025</v>
       </c>
@@ -6617,7 +6651,7 @@
         <v>1.6064714594964111</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" hidden="1">
       <c r="A167" s="3">
         <v>2025</v>
       </c>
@@ -6654,7 +6688,7 @@
         <v>1.8115529224108466</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" hidden="1">
       <c r="A168" s="3">
         <v>2025</v>
       </c>
@@ -6691,7 +6725,7 @@
         <v>2.8921744769984485</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" hidden="1">
       <c r="A169" s="3">
         <v>2025</v>
       </c>
@@ -6728,7 +6762,7 @@
         <v>1.9561616462607689</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" s="3">
         <v>2025</v>
       </c>
@@ -6765,7 +6799,7 @@
         <v>0.43864646234476468</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" s="3">
         <v>2025</v>
       </c>
@@ -6802,7 +6836,7 @@
         <v>1.7171500298192053</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" hidden="1">
       <c r="A172" s="3">
         <v>2025</v>
       </c>
@@ -6839,7 +6873,7 @@
         <v>4.4297595989518062</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" hidden="1">
       <c r="A173" s="3">
         <v>2025</v>
       </c>
@@ -6876,7 +6910,7 @@
         <v>1.9351276500644166</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" hidden="1">
       <c r="A174" s="3">
         <v>2025</v>
       </c>
@@ -6913,7 +6947,7 @@
         <v>1.4127834111883333</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" hidden="1">
       <c r="A175" s="3">
         <v>2025</v>
       </c>
@@ -6950,7 +6984,7 @@
         <v>1.6178648741027686</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" s="3">
         <v>2025</v>
       </c>
@@ -6987,7 +7021,7 @@
         <v>2.4714945530714014</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" hidden="1">
       <c r="A177" s="3">
         <v>2025</v>
       </c>
@@ -7024,7 +7058,7 @@
         <v>1.609100709020955</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" hidden="1">
       <c r="A178" s="3">
         <v>2025</v>
       </c>
@@ -7061,7 +7095,7 @@
         <v>0.43864646234476468</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" hidden="1">
       <c r="A179" s="3">
         <v>2025</v>
       </c>
@@ -7098,7 +7132,7 @@
         <v>1.8310841550204797</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" s="3">
         <v>2025</v>
       </c>
@@ -7135,7 +7169,7 @@
         <v>4.3568417454711179</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" s="3">
         <v>2025</v>
       </c>
@@ -7172,7 +7206,7 @@
         <v>1.8299576690826549</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" s="3">
         <v>2025</v>
       </c>
@@ -7209,7 +7243,7 @@
         <v>1.2988492651247578</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" hidden="1">
       <c r="A183" s="3">
         <v>2025</v>
       </c>
@@ -7246,7 +7280,7 @@
         <v>1.6520451179218412</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" hidden="1">
       <c r="A184" s="3">
         <v>2025</v>
       </c>
@@ -7283,7 +7317,7 @@
         <v>1.2725567698793174</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" hidden="1">
       <c r="A185" s="3">
         <v>2025</v>
       </c>
@@ -7320,7 +7354,7 @@
         <v>1.3146247622720222</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" hidden="1">
       <c r="A186" s="3">
         <v>2025</v>
       </c>
@@ -7357,7 +7391,7 @@
         <v>0.31331890167483195</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" s="3">
         <v>2025</v>
       </c>
@@ -7394,7 +7428,7 @@
         <v>1.4485910204162016</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" s="3">
         <v>2025</v>
       </c>
@@ -7431,7 +7465,7 @@
         <v>2.8984846758573544</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" s="3">
         <v>2025</v>
       </c>
@@ -7468,7 +7502,7 @@
         <v>1.2970964321083951</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" s="3">
         <v>2025</v>
       </c>
@@ -7505,7 +7539,7 @@
         <v>0.91147316850860205</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" s="3">
         <v>2025</v>
       </c>
@@ -7542,7 +7576,7 @@
         <v>1.2418821920929703</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" s="3">
         <v>2025</v>
       </c>
@@ -7579,7 +7613,7 @@
         <v>1.241005775584789</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" hidden="1">
       <c r="A193" s="3">
         <v>2025</v>
       </c>
@@ -7616,7 +7650,7 @@
         <v>1.2199717793884366</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" hidden="1">
       <c r="A194" s="3">
         <v>2025</v>
       </c>
@@ -7653,7 +7687,7 @@
         <v>0.39876951122251336</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" hidden="1">
       <c r="A195" s="3">
         <v>2025</v>
       </c>
@@ -7690,7 +7724,7 @@
         <v>1.5543869938173849</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" hidden="1">
       <c r="A196" s="3">
         <v>2025</v>
       </c>
@@ -7727,7 +7761,7 @@
         <v>2.7708784322661502</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" hidden="1">
       <c r="A197" s="3">
         <v>2025</v>
       </c>
@@ -7764,7 +7798,7 @@
         <v>1.1288244625375763</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" hidden="1">
       <c r="A198" s="3">
         <v>2025</v>
       </c>
@@ -7801,7 +7835,7 @@
         <v>0.92286658311495962</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" hidden="1">
       <c r="A199" s="3">
         <v>2025</v>
       </c>
@@ -7838,7 +7872,7 @@
         <v>1.0937678022103225</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" hidden="1">
       <c r="A200" s="3">
         <v>2025</v>
       </c>
@@ -7875,7 +7909,7 @@
         <v>1.0201488155230891</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" hidden="1">
       <c r="A201" s="3">
         <v>2025</v>
       </c>
@@ -7912,7 +7946,7 @@
         <v>0.82032585165774174</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" hidden="1">
       <c r="A202" s="3">
         <v>2025</v>
       </c>
@@ -7949,7 +7983,7 @@
         <v>0.42155634043522844</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" hidden="1">
       <c r="A203" s="3">
         <v>2025</v>
       </c>
@@ -7986,7 +8020,7 @@
         <v>1.4404528686161107</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" hidden="1">
       <c r="A204" s="3">
         <v>2025</v>
       </c>
@@ -8023,7 +8057,7 @@
         <v>3.9421214537997038</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" hidden="1">
       <c r="A205" s="3">
         <v>2025</v>
       </c>
@@ -8060,7 +8094,7 @@
         <v>1.6827196957081882</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" hidden="1">
       <c r="A206" s="3">
         <v>2025</v>
       </c>
@@ -8097,7 +8131,7 @@
         <v>0.85450609547681444</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" hidden="1">
       <c r="A207" s="3">
         <v>2025</v>
       </c>
@@ -8134,7 +8168,7 @@
         <v>1.0254073145721774</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" hidden="1">
       <c r="A208" s="3">
         <v>2025</v>
       </c>
@@ -8171,7 +8205,7 @@
         <v>0.93601283073767971</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" hidden="1">
       <c r="A209" s="3">
         <v>2025</v>
       </c>
@@ -8208,7 +8242,7 @@
         <v>1.1989377831920842</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" hidden="1">
       <c r="A210" s="3">
         <v>2025</v>
       </c>
@@ -8245,7 +8279,7 @@
         <v>0.31331890167483195</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" hidden="1">
       <c r="A211" s="3">
         <v>2025</v>
       </c>
@@ -8282,7 +8316,7 @@
         <v>1.147479403812834</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" hidden="1">
       <c r="A212" s="3">
         <v>2025</v>
       </c>
@@ -8319,7 +8353,7 @@
         <v>3.5547453571835481</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" hidden="1">
       <c r="A213" s="3">
         <v>2025</v>
       </c>
@@ -8356,7 +8390,7 @@
         <v>1.5512572194809862</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" hidden="1">
       <c r="A214" s="3">
         <v>2025</v>
       </c>
@@ -8393,7 +8427,7 @@
         <v>0.70639170559416664</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" hidden="1">
       <c r="A215" s="3">
         <v>2025</v>
       </c>
@@ -8430,7 +8464,7 @@
         <v>0.69499829098780908</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" hidden="1">
       <c r="A216" s="3">
         <v>2025</v>
       </c>
@@ -8467,7 +8501,7 @@
         <v>1.6827196957081882</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" hidden="1">
       <c r="A217" s="3">
         <v>2025</v>
       </c>
@@ -8504,7 +8538,7 @@
         <v>1.4513457375483123</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" hidden="1">
       <c r="A218" s="3">
         <v>2025</v>
       </c>
@@ -8541,7 +8575,7 @@
         <v>0.35319585279708327</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" hidden="1">
       <c r="A219" s="3">
         <v>2025</v>
       </c>
@@ -8578,7 +8612,7 @@
         <v>1.3183805916147453</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" hidden="1">
       <c r="A220" s="3">
         <v>2025</v>
       </c>
@@ -8615,7 +8649,7 @@
         <v>4.534579013330295</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" hidden="1">
       <c r="A221" s="3">
         <v>2025</v>
       </c>
@@ -8652,7 +8686,7 @@
         <v>2.0595787942261681</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" hidden="1">
       <c r="A222" s="3">
         <v>2025</v>
       </c>
@@ -8689,7 +8723,7 @@
         <v>0.92286658311495962</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" hidden="1">
       <c r="A223" s="3">
         <v>2025</v>
       </c>
@@ -8726,7 +8760,7 @@
         <v>0.7177851202005241</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" hidden="1">
       <c r="A224" s="3">
         <v>2025</v>
       </c>
@@ -8763,7 +8797,7 @@
         <v>1.3146247622720222</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" hidden="1">
       <c r="A225" s="3">
         <v>2025</v>
       </c>
@@ -8800,7 +8834,7 @@
         <v>2.5451135397586349</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" hidden="1">
       <c r="A226" s="3">
         <v>2025</v>
       </c>
@@ -8837,7 +8871,7 @@
         <v>0.43864646234476468</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" hidden="1">
       <c r="A227" s="3">
         <v>2025</v>
       </c>
@@ -8874,7 +8908,7 @@
         <v>1.521834386617021</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" hidden="1">
       <c r="A228" s="3">
         <v>2025</v>
       </c>
@@ -8911,7 +8945,7 @@
         <v>4.7624473054574459</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" hidden="1">
       <c r="A229" s="3">
         <v>2025</v>
       </c>
@@ -8948,7 +8982,7 @@
         <v>2.2173337656988106</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" hidden="1">
       <c r="A230" s="3">
         <v>2025</v>
       </c>
@@ -8985,7 +9019,7 @@
         <v>0.99122707075310479</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" hidden="1">
       <c r="A231" s="3">
         <v>2025</v>
       </c>
@@ -9022,7 +9056,7 @@
         <v>0.7747521932323117</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" hidden="1">
       <c r="A232" s="3">
         <v>2025</v>
       </c>
@@ -9059,7 +9093,7 @@
         <v>1.125318796504851</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" hidden="1">
       <c r="A233" s="3">
         <v>2025</v>
       </c>
@@ -9096,7 +9130,7 @@
         <v>2.6082155283476918</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" hidden="1">
       <c r="A234" s="3">
         <v>2025</v>
       </c>
@@ -9133,7 +9167,7 @@
         <v>0.51840036458926742</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" hidden="1">
       <c r="A235" s="3">
         <v>2025</v>
       </c>
@@ -9170,7 +9204,7 @@
         <v>1.8961893694212077</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" hidden="1">
       <c r="A236" s="3">
         <v>2025</v>
       </c>
@@ -9207,7 +9241,7 @@
         <v>6.1524438874330638</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" hidden="1">
       <c r="A237" s="3">
         <v>2025</v>
       </c>
@@ -9244,7 +9278,7 @@
         <v>2.5766645340531635</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" hidden="1">
       <c r="A238" s="3">
         <v>2025</v>
       </c>
@@ -9281,7 +9315,7 @@
         <v>1.5950780448900537</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" hidden="1">
       <c r="A239" s="3">
         <v>2025</v>
       </c>
@@ -9318,7 +9352,7 @@
         <v>1.2646690213056853</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" hidden="1">
       <c r="A240" s="3">
         <v>2025</v>
       </c>
@@ -9355,7 +9389,7 @@
         <v>0.8623938440504465</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" hidden="1">
       <c r="A241" s="3">
         <v>2025</v>
       </c>
@@ -9392,7 +9426,7 @@
         <v>3.207684419943734</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" hidden="1">
       <c r="A242" s="3">
         <v>2025</v>
       </c>
@@ -9429,7 +9463,7 @@
         <v>0.63233451065284263</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" hidden="1">
       <c r="A243" s="3">
         <v>2025</v>
       </c>
@@ -9466,7 +9500,7 @@
         <v>1.8636367622208438</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" hidden="1">
       <c r="A244" s="3">
         <v>2025</v>
       </c>
@@ -9503,7 +9537,7 @@
         <v>4.7852341346701603</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" hidden="1">
       <c r="A245" s="3">
         <v>2025</v>
       </c>
@@ -9540,7 +9574,7 @@
         <v>2.4802587181532152</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" hidden="1">
       <c r="A246" s="3">
         <v>2025</v>
       </c>
@@ -9577,7 +9611,7 @@
         <v>2.8255668223766666</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" hidden="1">
       <c r="A247" s="3">
         <v>2025</v>
       </c>
@@ -9614,7 +9648,7 @@
         <v>2.3812236527287229</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" hidden="1">
       <c r="A248" s="3">
         <v>2025</v>
       </c>
@@ -9651,7 +9685,7 @@
         <v>1.2199717793884366</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" hidden="1">
       <c r="A249" s="3">
         <v>2025</v>
       </c>
@@ -9688,7 +9722,7 @@
         <v>4.0069762754051235</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" hidden="1">
       <c r="A250" s="3">
         <v>2025</v>
       </c>
@@ -9725,7 +9759,7 @@
         <v>0.29053207246211687</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" hidden="1">
       <c r="A251" s="3">
         <v>2025</v>
       </c>
@@ -9762,7 +9796,7 @@
         <v>1.5055580830168389</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" hidden="1">
       <c r="A252" s="3">
         <v>2025</v>
       </c>
@@ -9799,7 +9833,7 @@
         <v>2.5293380426113705</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" hidden="1">
       <c r="A253" s="3">
         <v>2025</v>
       </c>
@@ -9836,7 +9870,7 @@
         <v>1.6739555306263749</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" hidden="1">
       <c r="A254" s="3">
         <v>2025</v>
       </c>
@@ -9873,7 +9907,7 @@
         <v>1.7773726785917741</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" hidden="1">
       <c r="A255" s="3">
         <v>2025</v>
       </c>
@@ -9910,7 +9944,7 @@
         <v>1.6520451179218412</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" hidden="1">
       <c r="A256" s="3">
         <v>2025</v>
       </c>
@@ -9947,7 +9981,7 @@
         <v>1.6301347052173074</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" hidden="1">
       <c r="A257" s="3">
         <v>2025</v>
       </c>
@@ -9984,7 +10018,7 @@
         <v>2.9763104617838581</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" hidden="1">
       <c r="A258" s="3">
         <v>2025</v>
       </c>
@@ -10021,7 +10055,7 @@
         <v>0.24495841403668678</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" hidden="1">
       <c r="A259" s="3">
         <v>2025</v>
       </c>
@@ -10058,7 +10092,7 @@
         <v>1.4974199312167478</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" hidden="1">
       <c r="A260" s="3">
         <v>2025</v>
       </c>
@@ -10095,7 +10129,7 @@
         <v>2.734419505525806</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" hidden="1">
       <c r="A261" s="3">
         <v>2025</v>
       </c>
@@ -10132,7 +10166,7 @@
         <v>1.4811438988264782</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" hidden="1">
       <c r="A262" s="3">
         <v>2025</v>
       </c>
@@ -10169,7 +10203,7 @@
         <v>1.4811438988264785</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" hidden="1">
       <c r="A263" s="3">
         <v>2025</v>
       </c>
@@ -10206,7 +10240,7 @@
         <v>1.4241768257946907</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" hidden="1">
       <c r="A264" s="3">
         <v>2025</v>
       </c>
@@ -10243,7 +10277,7 @@
         <v>1.3461757565665506</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" hidden="1">
       <c r="A265" s="3">
         <v>2025</v>
       </c>
@@ -10280,7 +10314,7 @@
         <v>2.7870044960166869</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" hidden="1">
       <c r="A266" s="3">
         <v>2025</v>
       </c>
@@ -10317,7 +10351,7 @@
         <v>0.27344195055258058</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" hidden="1">
       <c r="A267" s="3">
         <v>2025</v>
       </c>
@@ -10354,7 +10388,7 @@
         <v>1.2451372254139261</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" hidden="1">
       <c r="A268" s="3">
         <v>2025</v>
       </c>
@@ -10391,7 +10425,7 @@
         <v>3.0078614560783867</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" hidden="1">
       <c r="A269" s="3">
         <v>2025</v>
       </c>
@@ -10428,7 +10462,7 @@
         <v>1.5249647242355457</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" hidden="1">
       <c r="A270" s="3">
         <v>2025</v>
       </c>
@@ -10465,7 +10499,7 @@
         <v>1.8343397516235616</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" hidden="1">
       <c r="A271" s="3">
         <v>2025</v>
       </c>
@@ -10502,7 +10536,7 @@
         <v>1.8115529224108466</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" hidden="1">
       <c r="A272" s="3">
         <v>2025</v>
       </c>
@@ -10539,7 +10573,7 @@
         <v>1.850991665279007</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" hidden="1">
       <c r="A273" s="3">
         <v>2025</v>
       </c>
@@ -10576,7 +10610,7 @@
         <v>2.4399435587768732</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" hidden="1">
       <c r="A274" s="3">
         <v>2025</v>
       </c>
@@ -10613,7 +10647,7 @@
         <v>0.26774524324940185</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" hidden="1">
       <c r="A275" s="3">
         <v>2025</v>
       </c>
@@ -10650,7 +10684,7 @@
         <v>1.0742360376120148</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" hidden="1">
       <c r="A276" s="3">
         <v>2025</v>
       </c>
@@ -10687,7 +10721,7 @@
         <v>2.4609775549732253</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" hidden="1">
       <c r="A277" s="3">
         <v>2025</v>
       </c>
@@ -10724,7 +10758,7 @@
         <v>1.200690616208447</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" hidden="1">
       <c r="A278" s="3">
         <v>2025</v>
       </c>
@@ -10761,7 +10795,7 @@
         <v>2.1077817021761422</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" hidden="1">
       <c r="A279" s="3">
         <v>2025</v>
       </c>
@@ -10798,7 +10832,7 @@
         <v>2.4154038965477955</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" hidden="1">
       <c r="A280" s="3">
         <v>2025</v>
       </c>
@@ -10835,7 +10869,7 @@
         <v>2.250637593009702</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" hidden="1">
       <c r="A281" s="3">
         <v>2025</v>
       </c>
@@ -10872,7 +10906,7 @@
         <v>2.1875356044206447</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" hidden="1">
       <c r="A282" s="3">
         <v>2025</v>
       </c>
@@ -10909,7 +10943,7 @@
         <v>0.22786829212715048</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" hidden="1">
       <c r="A283" s="3">
         <v>2025</v>
       </c>
@@ -10946,7 +10980,7 @@
         <v>1.3753476542153824</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" hidden="1">
       <c r="A284" s="3">
         <v>2025</v>
       </c>
@@ -10983,7 +11017,7 @@
         <v>2.7116326763130911</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" hidden="1">
       <c r="A285" s="3">
         <v>2025</v>
       </c>
@@ -11020,7 +11054,7 @@
         <v>1.5512572194809862</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" hidden="1">
       <c r="A286" s="3">
         <v>2025</v>
       </c>
@@ -11057,7 +11091,7 @@
         <v>1.538110971858266</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" hidden="1">
       <c r="A287" s="3">
         <v>2025</v>
       </c>
@@ -11094,7 +11128,7 @@
         <v>1.8343397516235616</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" hidden="1">
       <c r="A288" s="3">
         <v>2025</v>
       </c>
@@ -11131,7 +11165,7 @@
         <v>2.0718486253407069</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" hidden="1">
       <c r="A289" s="3">
         <v>2025</v>
       </c>
@@ -11168,7 +11202,7 @@
         <v>2.1244336158315877</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" hidden="1">
       <c r="A290" s="3">
         <v>2025</v>
       </c>
@@ -11205,7 +11239,7 @@
         <v>0.19368804830807793</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" hidden="1">
       <c r="A291" s="3">
         <v>2025</v>
       </c>
@@ -11242,7 +11276,7 @@
         <v>1.9043275212212989</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" hidden="1">
       <c r="A292" s="3">
         <v>2025</v>
       </c>
@@ -11279,7 +11313,7 @@
         <v>3.4180243819072578</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" hidden="1">
       <c r="A293" s="3">
         <v>2025</v>
       </c>
@@ -11316,7 +11350,7 @@
         <v>1.5600213845627995</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" hidden="1">
       <c r="A294" s="3">
         <v>2025</v>
       </c>
@@ -11353,7 +11387,7 @@
         <v>1.3558163381565456</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" hidden="1">
       <c r="A295" s="3">
         <v>2025</v>
       </c>
@@ -11390,7 +11424,7 @@
         <v>1.4127834111883333</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" hidden="1">
       <c r="A296" s="3">
         <v>2025</v>
       </c>
@@ -11427,7 +11461,7 @@
         <v>2.5871815321513396</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" hidden="1">
       <c r="A297" s="3">
         <v>2025</v>
       </c>
@@ -11464,7 +11498,7 @@
         <v>1.8615086633771833</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" hidden="1">
       <c r="A298" s="3">
         <v>2025</v>
       </c>
@@ -11501,7 +11535,7 @@
         <v>0.39307280391933458</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" hidden="1">
       <c r="A299" s="3">
         <v>2025</v>
       </c>
@@ -11538,7 +11572,7 @@
         <v>2.1403339234239382</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" hidden="1">
       <c r="A300" s="3">
         <v>2025</v>
       </c>
@@ -11575,7 +11609,7 @@
         <v>4.6029395009684402</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" hidden="1">
       <c r="A301" s="3">
         <v>2025</v>
       </c>
@@ -11612,7 +11646,7 @@
         <v>2.0946354545534218</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" hidden="1">
       <c r="A302" s="3">
         <v>2025</v>
       </c>
@@ -11649,7 +11683,7 @@
         <v>1.5950780448900537</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" hidden="1">
       <c r="A303" s="3">
         <v>2025</v>
       </c>
@@ -11686,7 +11720,7 @@
         <v>1.8685199954426341</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" hidden="1">
       <c r="A304" s="3">
         <v>2025</v>
       </c>
@@ -11723,7 +11757,7 @@
         <v>2.6713175169367491</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" hidden="1">
       <c r="A305" s="3">
         <v>2025</v>
       </c>
@@ -11760,7 +11794,7 @@
         <v>2.1770186063224686</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" hidden="1">
       <c r="A306" s="3">
         <v>2025</v>
       </c>
@@ -11797,7 +11831,7 @@
         <v>0.35319585279708327</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" hidden="1">
       <c r="A307" s="3">
         <v>2025</v>
       </c>
@@ -11834,7 +11868,7 @@
         <v>1.9450182802217539</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" hidden="1">
       <c r="A308" s="3">
         <v>2025</v>
       </c>
@@ -11871,7 +11905,7 @@
         <v>3.7598268200979832</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" hidden="1">
       <c r="A309" s="3">
         <v>2025</v>
       </c>
@@ -11908,7 +11942,7 @@
         <v>1.805418006853577</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" hidden="1">
       <c r="A310" s="3">
         <v>2025</v>
       </c>
@@ -11945,7 +11979,7 @@
         <v>2.2672895066651475</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" hidden="1">
       <c r="A311" s="3">
         <v>2025</v>
       </c>
@@ -11982,7 +12016,7 @@
         <v>2.358436823516008</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" hidden="1">
       <c r="A312" s="3">
         <v>2025</v>
       </c>
@@ -12019,7 +12053,7 @@
         <v>2.4714945530714014</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" hidden="1">
       <c r="A313" s="3">
         <v>2025</v>
       </c>
@@ -12056,7 +12090,7 @@
         <v>2.2190865987151733</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" hidden="1">
       <c r="A314" s="3">
         <v>2025</v>
       </c>
@@ -12093,7 +12127,7 @@
         <v>0.29622877976529566</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" hidden="1">
       <c r="A315" s="3">
         <v>2025</v>
       </c>
@@ -12130,7 +12164,7 @@
         <v>2.1728865306243024</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" hidden="1">
       <c r="A316" s="3">
         <v>2025</v>
       </c>
@@ -12167,7 +12201,7 @@
         <v>4.4890053549048652</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" hidden="1">
       <c r="A317" s="3">
         <v>2025</v>
       </c>
@@ -12204,7 +12238,7 @@
         <v>2.1735129402897431</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" hidden="1">
       <c r="A318" s="3">
         <v>2025</v>
       </c>
@@ -12241,7 +12275,7 @@
         <v>2.0052409707189245</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" hidden="1">
       <c r="A319" s="3">
         <v>2025</v>
       </c>
@@ -12278,7 +12312,7 @@
         <v>1.9824541415062096</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" hidden="1">
       <c r="A320" s="3">
         <v>2025</v>
       </c>
@@ -12315,7 +12349,7 @@
         <v>1.9561616462607689</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" hidden="1">
       <c r="A321" s="3">
         <v>2025</v>
       </c>
@@ -12352,7 +12386,7 @@
         <v>2.4714945530714014</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" hidden="1">
       <c r="A322" s="3">
         <v>2025</v>
       </c>
@@ -12389,7 +12423,7 @@
         <v>0.21647487752079297</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" hidden="1">
       <c r="A323" s="3">
         <v>2025</v>
       </c>
@@ -12426,7 +12460,7 @@
         <v>1.7497026370195694</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" hidden="1">
       <c r="A324" s="3">
         <v>2025</v>
       </c>
@@ -12463,7 +12497,7 @@
         <v>3.053435114503817</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" hidden="1">
       <c r="A325" s="3">
         <v>2025</v>
       </c>
@@ -12500,7 +12534,7 @@
         <v>1.4899080639082918</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" hidden="1">
       <c r="A326" s="3">
         <v>2025</v>
       </c>
@@ -12537,7 +12571,7 @@
         <v>1.3444229235501881</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" hidden="1">
       <c r="A327" s="3">
         <v>2025</v>
       </c>
@@ -12574,7 +12608,7 @@
         <v>1.4469636550074059</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" hidden="1">
       <c r="A328" s="3">
         <v>2025</v>
       </c>
@@ -12611,7 +12645,7 @@
         <v>2.1244336158315877</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" hidden="1">
       <c r="A329" s="3">
         <v>2025</v>
       </c>
@@ -12648,7 +12682,7 @@
         <v>2.3032225835005828</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" hidden="1">
       <c r="A330" s="3">
         <v>2025</v>
       </c>
@@ -12685,7 +12719,7 @@
         <v>0.20508146291443544</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" hidden="1">
       <c r="A331" s="3">
         <v>2025</v>
       </c>
@@ -12722,7 +12756,7 @@
         <v>1.2776898326142903</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" hidden="1">
       <c r="A332" s="3">
         <v>2025</v>
       </c>
@@ -12759,7 +12793,7 @@
         <v>2.9850746268656718</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" hidden="1">
       <c r="A333" s="3">
         <v>2025</v>
       </c>
@@ -12796,7 +12830,7 @@
         <v>1.7265405211172558</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" hidden="1">
       <c r="A334" s="3">
         <v>2025</v>
       </c>
@@ -12833,7 +12867,7 @@
         <v>0.91147316850860205</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" hidden="1">
       <c r="A335" s="3">
         <v>2025</v>
       </c>
@@ -12870,7 +12904,7 @@
         <v>0.84311268087045688</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" hidden="1">
       <c r="A336" s="3">
         <v>2025</v>
       </c>
@@ -12907,7 +12941,7 @@
         <v>1.9351276500644166</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" hidden="1">
       <c r="A337" s="3">
         <v>2025</v>
       </c>
@@ -12944,7 +12978,7 @@
         <v>2.8290724884093916</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" hidden="1">
       <c r="A338" s="3">
         <v>2025</v>
       </c>
@@ -12981,7 +13015,7 @@
         <v>0.34749914549390448</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" hidden="1">
       <c r="A339" s="3">
         <v>2025</v>
       </c>
@@ -13018,7 +13052,7 @@
         <v>1.3509331988151094</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" hidden="1">
       <c r="A340" s="3">
         <v>2025</v>
       </c>
@@ -13055,7 +13089,7 @@
         <v>3.3496638942691126</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" hidden="1">
       <c r="A341" s="3">
         <v>2025</v>
       </c>
@@ -13092,7 +13126,7 @@
         <v>1.4373230734174109</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" hidden="1">
       <c r="A342" s="3">
         <v>2025</v>
       </c>
@@ -13129,7 +13163,7 @@
         <v>0.99122707075310479</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" hidden="1">
       <c r="A343" s="3">
         <v>2025</v>
       </c>
@@ -13166,7 +13200,7 @@
         <v>0.92286658311495962</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" hidden="1">
       <c r="A344" s="3">
         <v>2025</v>
       </c>
@@ -13203,7 +13237,7 @@
         <v>1.7668556804935978</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" hidden="1">
       <c r="A345" s="3">
         <v>2025</v>
       </c>
@@ -13240,7 +13274,7 @@
         <v>2.965793463685682</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" hidden="1">
       <c r="A346" s="3">
         <v>2025</v>
       </c>
@@ -13277,7 +13311,7 @@
         <v>0.38737609661615585</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" hidden="1">
       <c r="A347" s="3">
         <v>2025</v>
       </c>
@@ -13314,7 +13348,7 @@
         <v>1.4730054758164748</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" hidden="1">
       <c r="A348" s="3">
         <v>2025</v>
       </c>
@@ -13351,7 +13385,7 @@
         <v>4.1927765751395691</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" hidden="1">
       <c r="A349" s="3">
         <v>2025</v>
       </c>
@@ -13388,7 +13422,7 @@
         <v>2.2173337656988106</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" hidden="1">
       <c r="A350" s="3">
         <v>2025</v>
       </c>
@@ -13425,7 +13459,7 @@
         <v>1.4925373134328359</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" hidden="1">
       <c r="A351" s="3">
         <v>2025</v>
       </c>
@@ -13462,7 +13496,7 @@
         <v>1.6862253617409138</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" hidden="1">
       <c r="A352" s="3">
         <v>2025</v>
       </c>
@@ -13499,7 +13533,7 @@
         <v>1.367209752762903</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" hidden="1">
       <c r="A353" s="3">
         <v>2025</v>
       </c>
@@ -13536,7 +13570,7 @@
         <v>3.1550994294528532</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" hidden="1">
       <c r="A354" s="3">
         <v>2025</v>
       </c>
@@ -13573,7 +13607,7 @@
         <v>0.39876951122251336</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" hidden="1">
       <c r="A355" s="3">
         <v>2025</v>
       </c>
@@ -13610,7 +13644,7 @@
         <v>1.3509331988151094</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" hidden="1">
       <c r="A356" s="3">
         <v>2025</v>
       </c>
@@ -13647,7 +13681,7 @@
         <v>2.734419505525806</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" hidden="1">
       <c r="A357" s="3">
         <v>2025</v>
       </c>
@@ -13684,7 +13718,7 @@
         <v>1.568785549644613</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" hidden="1">
       <c r="A358" s="3">
         <v>2025</v>
       </c>
@@ -13721,7 +13755,7 @@
         <v>1.6862253617409138</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" hidden="1">
       <c r="A359" s="3">
         <v>2025</v>
       </c>
@@ -13758,7 +13792,7 @@
         <v>1.4241768257946907</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" hidden="1">
       <c r="A360" s="3">
         <v>2025</v>
       </c>
@@ -13795,7 +13829,7 @@
         <v>1.2515227736829651</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" hidden="1">
       <c r="A361" s="3">
         <v>2025</v>
       </c>
@@ -13832,7 +13866,7 @@
         <v>2.6608005188385726</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" hidden="1">
       <c r="A362" s="3">
         <v>2025</v>
       </c>
@@ -13869,7 +13903,7 @@
         <v>0.30192548706847439</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" hidden="1">
       <c r="A363" s="3">
         <v>2025</v>
       </c>
@@ -13906,7 +13940,7 @@
         <v>1.3672095024152915</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" hidden="1">
       <c r="A364" s="3">
         <v>2025</v>
       </c>
@@ -13943,7 +13977,7 @@
         <v>1.8913068246553493</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" hidden="1">
       <c r="A365" s="3">
         <v>2025</v>
       </c>
@@ -13980,7 +14014,7 @@
         <v>1.2532756066993278</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" hidden="1">
       <c r="A366" s="3">
         <v>2025</v>
       </c>
@@ -14017,7 +14051,7 @@
         <v>1.6520451179218412</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" hidden="1">
       <c r="A367" s="3">
         <v>2025</v>
       </c>
@@ -14054,7 +14088,7 @@
         <v>1.6292582887091263</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" hidden="1">
       <c r="A368" s="3">
         <v>2025</v>
       </c>
@@ -14091,7 +14125,7 @@
         <v>0.82032585165774174</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" hidden="1">
       <c r="A369" s="3">
         <v>2025</v>
       </c>
@@ -14128,7 +14162,7 @@
         <v>2.2611545911078781</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" hidden="1">
       <c r="A370" s="3">
         <v>2025</v>
       </c>
@@ -14165,7 +14199,7 @@
         <v>0.48422012077019483</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" hidden="1">
       <c r="A371" s="3">
         <v>2025</v>
       </c>
@@ -14202,7 +14236,7 @@
         <v>1.3265187434148364</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" hidden="1">
       <c r="A372" s="3">
         <v>2025</v>
       </c>
@@ -14239,7 +14273,7 @@
         <v>2.9395009684402416</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" hidden="1">
       <c r="A373" s="3">
         <v>2025</v>
       </c>
@@ -14276,7 +14310,7 @@
         <v>1.770361346526323</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" hidden="1">
       <c r="A374" s="3">
         <v>2025</v>
       </c>
@@ -14313,7 +14347,7 @@
         <v>1.9027002392617067</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" hidden="1">
       <c r="A375" s="3">
         <v>2025</v>
       </c>
@@ -14350,7 +14384,7 @@
         <v>1.8913068246553493</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" hidden="1">
       <c r="A376" s="3">
         <v>2025</v>
       </c>
@@ -14387,7 +14421,7 @@
         <v>1.2620397717811411</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" hidden="1">
       <c r="A377" s="3">
         <v>2025</v>
       </c>
@@ -14424,7 +14458,7 @@
         <v>2.4189095625805206</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" hidden="1">
       <c r="A378" s="3">
         <v>2025</v>
       </c>
@@ -14461,7 +14495,7 @@
         <v>0.46143329155747975</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" hidden="1">
       <c r="A379" s="3">
         <v>2025</v>
       </c>
@@ -14498,7 +14532,7 @@
         <v>1.5299725384171119</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" hidden="1">
       <c r="A380" s="3">
         <v>2025</v>
       </c>
@@ -14535,7 +14569,7 @@
         <v>3.3724507234818275</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" hidden="1">
       <c r="A381" s="3">
         <v>2025</v>
       </c>
@@ -14572,7 +14606,7 @@
         <v>1.8580029973444578</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" hidden="1">
       <c r="A382" s="3">
         <v>2025</v>
       </c>
@@ -14609,7 +14643,7 @@
         <v>1.6406517033154837</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" hidden="1">
       <c r="A383" s="3">
         <v>2025</v>
       </c>
@@ -14646,7 +14680,7 @@
         <v>1.5153241426455508</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" hidden="1">
       <c r="A384" s="3">
         <v>2025</v>
       </c>
@@ -14683,7 +14717,7 @@
         <v>2.1244336158315877</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" hidden="1">
       <c r="A385" s="3">
         <v>2025</v>
       </c>
@@ -14720,7 +14754,7 @@
         <v>2.6923515131331013</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" hidden="1">
       <c r="A386" s="3">
         <v>2025</v>
       </c>
@@ -14757,7 +14791,7 @@
         <v>0.39876951122251336</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" hidden="1">
       <c r="A387" s="3">
         <v>2025</v>
       </c>
@@ -14794,7 +14828,7 @@
         <v>1.8473604586206618</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" hidden="1">
       <c r="A388" s="3">
         <v>2025</v>
       </c>
@@ -14831,7 +14865,7 @@
         <v>3.167369260567392</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" hidden="1">
       <c r="A389" s="3">
         <v>2025</v>
       </c>
@@ -14868,7 +14902,7 @@
         <v>1.6739555306263749</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" hidden="1">
       <c r="A390" s="3">
         <v>2025</v>
       </c>
@@ -14905,7 +14939,7 @@
         <v>1.5039307280391934</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" hidden="1">
       <c r="A391" s="3">
         <v>2025</v>
       </c>
@@ -14942,7 +14976,7 @@
         <v>1.4925373134328359</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" hidden="1">
       <c r="A392" s="3">
         <v>2025</v>
       </c>
@@ -14979,7 +15013,7 @@
         <v>2.1454676120279399</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" hidden="1">
       <c r="A393" s="3">
         <v>2025</v>
       </c>
@@ -15016,7 +15050,7 @@
         <v>1.598583710922779</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" hidden="1">
       <c r="A394" s="3">
         <v>2025</v>
       </c>
@@ -15053,7 +15087,7 @@
         <v>0.26204853594622307</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" hidden="1">
       <c r="A395" s="3">
         <v>2025</v>
       </c>
@@ -15090,7 +15124,7 @@
         <v>1.7090118780191144</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" hidden="1">
       <c r="A396" s="3">
         <v>2025</v>
       </c>
@@ -15127,7 +15161,7 @@
         <v>4.2155634043522845</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" hidden="1">
       <c r="A397" s="3">
         <v>2025</v>
       </c>
@@ -15164,7 +15198,7 @@
         <v>2.3838529022532668</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" hidden="1">
       <c r="A398" s="3">
         <v>2025</v>
       </c>
@@ -15201,7 +15235,7 @@
         <v>1.8685199954426341</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" hidden="1">
       <c r="A399" s="3">
         <v>2025</v>
       </c>
@@ -15238,7 +15272,7 @@
         <v>2.0280277999316394</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" hidden="1">
       <c r="A400" s="3">
         <v>2025</v>
       </c>
@@ -15275,7 +15309,7 @@
         <v>3.8281873077361284</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" hidden="1">
       <c r="A401" s="3">
         <v>2025</v>
       </c>
@@ -15312,7 +15346,7 @@
         <v>2.082365623438883</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" hidden="1">
       <c r="A402" s="3">
         <v>2025</v>
       </c>
@@ -15349,7 +15383,7 @@
         <v>1.7090121909536286E-2</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" hidden="1">
       <c r="A403" s="3">
         <v>2025</v>
       </c>
@@ -15386,7 +15420,7 @@
         <v>1.7334263334193873</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" hidden="1">
       <c r="A404" s="3">
         <v>2025</v>
       </c>
@@ -15423,7 +15457,7 @@
         <v>3.4408112111199727</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" hidden="1">
       <c r="A405" s="3">
         <v>2025</v>
       </c>
@@ -15460,7 +15494,7 @@
         <v>1.3409172575174626</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" hidden="1">
       <c r="A406" s="3">
         <v>2025</v>
       </c>
@@ -15497,7 +15531,7 @@
         <v>1.9027002392617067</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" hidden="1">
       <c r="A407" s="3">
         <v>2025</v>
       </c>
@@ -15534,7 +15568,7 @@
         <v>1.6634385325281988</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" hidden="1">
       <c r="A408" s="3">
         <v>2025</v>
       </c>
@@ -15571,7 +15605,7 @@
         <v>2.0402976310461782</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" hidden="1">
       <c r="A409" s="3">
         <v>2025</v>
       </c>
@@ -15608,7 +15642,7 @@
         <v>2.2190865987151733</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" hidden="1">
       <c r="A410" s="3">
         <v>2025</v>
       </c>
@@ -15645,7 +15679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" hidden="1">
       <c r="A411" s="3">
         <v>2025</v>
       </c>
@@ -15682,7 +15716,7 @@
         <v>1.9450182802217539</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" hidden="1">
       <c r="A412" s="3">
         <v>2025</v>
       </c>
@@ -15719,7 +15753,7 @@
         <v>4.1699897459268547</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" hidden="1">
       <c r="A413" s="3">
         <v>2025</v>
       </c>
@@ -15756,7 +15790,7 @@
         <v>2.0858712894716085</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" hidden="1">
       <c r="A414" s="3">
         <v>2025</v>
       </c>
@@ -15793,7 +15827,7 @@
         <v>2.1305685313888572</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" hidden="1">
       <c r="A415" s="3">
         <v>2025</v>
       </c>
@@ -15830,7 +15864,7 @@
         <v>1.8799134100489918</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" hidden="1">
       <c r="A416" s="3">
         <v>2025</v>
       </c>
@@ -15867,7 +15901,7 @@
         <v>2.1033996196352356</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" hidden="1">
       <c r="A417" s="3">
         <v>2025</v>
       </c>
@@ -15904,7 +15938,7 @@
         <v>2.5976985302495157</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" hidden="1">
       <c r="A418" s="3">
         <v>2026</v>
       </c>
@@ -15941,7 +15975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" hidden="1">
       <c r="A419" s="3">
         <v>2026</v>
       </c>
@@ -15978,7 +16012,7 @@
         <v>1.5299725384171119</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" hidden="1">
       <c r="A420" s="3">
         <v>2026</v>
       </c>
@@ -16015,7 +16049,7 @@
         <v>6.1752307166457792</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" hidden="1">
       <c r="A421" s="3">
         <v>2026</v>
       </c>
@@ -16052,7 +16086,7 @@
         <v>2.5679003689713498</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" hidden="1">
       <c r="A422" s="3">
         <v>2026</v>
       </c>
@@ -16089,7 +16123,7 @@
         <v>1.8799134100489918</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" hidden="1">
       <c r="A423" s="3">
         <v>2026</v>
       </c>
@@ -16126,7 +16160,7 @@
         <v>1.6976187763472714</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" hidden="1">
       <c r="A424" s="3">
         <v>2026</v>
       </c>
@@ -16163,7 +16197,7 @@
         <v>3.5442283590853716</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" hidden="1">
       <c r="A425" s="3">
         <v>2026</v>
       </c>
@@ -16200,7 +16234,7 @@
         <v>2.0928826215370591</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" hidden="1">
       <c r="A426" s="3">
         <v>2026</v>
       </c>
@@ -16237,7 +16271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" hidden="1">
       <c r="A427" s="3">
         <v>2026</v>
       </c>
@@ -16274,7 +16308,7 @@
         <v>1.3427950470150185</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" hidden="1">
       <c r="A428" s="3">
         <v>2026</v>
       </c>
@@ -16311,7 +16345,7 @@
         <v>4.6257263301811555</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" hidden="1">
       <c r="A429" s="3">
         <v>2026</v>
       </c>
@@ -16348,7 +16382,7 @@
         <v>1.638898870299121</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" hidden="1">
       <c r="A430" s="3">
         <v>2026</v>
       </c>
@@ -16385,7 +16419,7 @@
         <v>1.9368804830807793</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" hidden="1">
       <c r="A431" s="3">
         <v>2026</v>
       </c>
@@ -16422,7 +16456,7 @@
         <v>1.9368804830807793</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" hidden="1">
       <c r="A432" s="3">
         <v>2026</v>
       </c>
@@ -16459,7 +16493,7 @@
         <v>2.1349506139297638</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" hidden="1">
       <c r="A433" s="3">
         <v>2026</v>
       </c>
@@ -16496,7 +16530,7 @@
         <v>2.6082155283476918</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" hidden="1">
       <c r="A434" s="3">
         <v>2026</v>
       </c>
@@ -16533,7 +16567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" hidden="1">
       <c r="A435" s="3">
         <v>2026</v>
       </c>
@@ -16570,7 +16604,7 @@
         <v>1.4323147168160197</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" hidden="1">
       <c r="A436" s="3">
         <v>2026</v>
       </c>
@@ -16607,7 +16641,7 @@
         <v>5.8790019368804831</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" hidden="1">
       <c r="A437" s="3">
         <v>2026</v>
       </c>
@@ -16644,7 +16678,7 @@
         <v>2.602957029298604</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" hidden="1">
       <c r="A438" s="3">
         <v>2026</v>
       </c>
@@ -16681,7 +16715,7 @@
         <v>1.4013899965819756</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" hidden="1">
       <c r="A439" s="3">
         <v>2026</v>
       </c>
@@ -16718,7 +16752,7 @@
         <v>1.2988492651247578</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" hidden="1">
       <c r="A440" s="3">
         <v>2026</v>
       </c>
@@ -16755,7 +16789,7 @@
         <v>1.2830737679774935</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" hidden="1">
       <c r="A441" s="3">
         <v>2026</v>
       </c>
@@ -16792,7 +16826,7 @@
         <v>2.8501064846057438</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" hidden="1">
       <c r="A442" s="3">
         <v>2026</v>
       </c>
@@ -16829,7 +16863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" hidden="1">
       <c r="A443" s="3">
         <v>2026</v>
       </c>
@@ -16866,7 +16900,7 @@
         <v>1.9938471910223001</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" hidden="1">
       <c r="A444" s="3">
         <v>2026</v>
       </c>
@@ -16903,7 +16937,7 @@
         <v>9.9350575367437628</v>
       </c>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" hidden="1">
       <c r="A445" s="3">
         <v>2026</v>
       </c>
@@ -16940,7 +16974,7 @@
         <v>2.9009386420802623</v>
       </c>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" hidden="1">
       <c r="A446" s="3">
         <v>2026</v>
       </c>
@@ -16977,7 +17011,7 @@
         <v>3.3496638942691126</v>
       </c>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" hidden="1">
       <c r="A447" s="3">
         <v>2026</v>
       </c>
@@ -17014,7 +17048,7 @@
         <v>3.053435114503817</v>
       </c>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" hidden="1">
       <c r="A448" s="3">
         <v>2026</v>
       </c>
@@ -17051,7 +17085,7 @@
         <v>4.0595612658960043</v>
       </c>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" hidden="1">
       <c r="A449" s="3">
         <v>2026</v>
       </c>
@@ -17088,7 +17122,7 @@
         <v>5.6160769844260781</v>
       </c>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" hidden="1">
       <c r="A450" s="3">
         <v>2026</v>
       </c>
@@ -17125,7 +17159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" hidden="1">
       <c r="A451" s="3">
         <v>2026</v>
       </c>
@@ -17162,7 +17196,7 @@
         <v>3.3854711488378646</v>
       </c>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" hidden="1">
       <c r="A452" s="3">
         <v>2026</v>
       </c>
@@ -17199,7 +17233,7 @@
         <v>6.8816224222399454</v>
       </c>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" hidden="1">
       <c r="A453" s="3">
         <v>2026</v>
       </c>
@@ -17236,7 +17270,7 @@
         <v>3.970166782061507</v>
       </c>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" hidden="1">
       <c r="A454" s="3">
         <v>2026</v>
       </c>
@@ -17273,7 +17307,7 @@
         <v>5.8448216930614105</v>
       </c>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" hidden="1">
       <c r="A455" s="3">
         <v>2026</v>
       </c>
@@ -17310,7 +17344,7 @@
         <v>5.0131024267973112</v>
       </c>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" hidden="1">
       <c r="A456" s="3">
         <v>2026</v>
       </c>
@@ -17347,7 +17381,7 @@
         <v>3.1971674218455579</v>
       </c>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" hidden="1">
       <c r="A457" s="3">
         <v>2026</v>
       </c>
@@ -17384,7 +17418,7 @@
         <v>6.4784708284765253</v>
       </c>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" hidden="1">
       <c r="A458" s="3">
         <v>2026</v>
       </c>
@@ -17421,7 +17455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" hidden="1">
       <c r="A459" s="3">
         <v>2026</v>
       </c>
@@ -17458,7 +17492,7 @@
         <v>2.5716559688287624</v>
       </c>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" hidden="1">
       <c r="A460" s="3">
         <v>2026</v>
       </c>
@@ -17495,7 +17529,7 @@
         <v>2.8027799931639512</v>
       </c>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" hidden="1">
       <c r="A461" s="3">
         <v>2026</v>
       </c>
@@ -17532,7 +17566,7 @@
         <v>1.0166431494903638</v>
       </c>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" hidden="1">
       <c r="A462" s="3">
         <v>2026</v>
       </c>
@@ -17569,7 +17603,7 @@
         <v>2.7002392617067335</v>
       </c>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" hidden="1">
       <c r="A463" s="3">
         <v>2026</v>
       </c>
@@ -17606,7 +17640,7 @@
         <v>2.3812236527287229</v>
       </c>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" hidden="1">
       <c r="A464" s="3">
         <v>2026</v>
       </c>
@@ -17643,7 +17677,7 @@
         <v>1.9877126405552974</v>
       </c>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" hidden="1">
       <c r="A465" s="3">
         <v>2026</v>
       </c>
@@ -17680,7 +17714,7 @@
         <v>2.8921744769984485</v>
       </c>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" hidden="1">
       <c r="A466" s="3">
         <v>2026</v>
       </c>
@@ -17717,7 +17751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" hidden="1">
       <c r="A467" s="3">
         <v>2026</v>
       </c>
@@ -17754,7 +17788,7 @@
         <v>2.0589524054230282</v>
       </c>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" hidden="1">
       <c r="A468" s="3">
         <v>2026</v>
       </c>
@@ -17791,7 +17825,7 @@
         <v>2.1647487752079297</v>
       </c>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" hidden="1">
       <c r="A469" s="3">
         <v>2026</v>
       </c>
@@ -17828,7 +17862,7 @@
         <v>1.568785549644613</v>
       </c>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" hidden="1">
       <c r="A470" s="3">
         <v>2026</v>
       </c>
@@ -17865,7 +17899,7 @@
         <v>2.6546656032813036</v>
       </c>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" hidden="1">
       <c r="A471" s="3">
         <v>2026</v>
       </c>
@@ -17902,7 +17936,7 @@
         <v>2.8369602369830238</v>
       </c>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" hidden="1">
       <c r="A472" s="3">
         <v>2026</v>
       </c>
@@ -17939,7 +17973,7 @@
         <v>1.850991665279007</v>
       </c>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" hidden="1">
       <c r="A473" s="3">
         <v>2026</v>
       </c>
@@ -17976,7 +18010,7 @@
         <v>3.3233713990236717</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" hidden="1">
       <c r="A474" s="3">
         <v>2026</v>
       </c>
@@ -18013,7 +18047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" hidden="1">
       <c r="A475" s="3">
         <v>2026</v>
       </c>
@@ -18050,7 +18084,7 @@
         <v>1.4811436276165657</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" hidden="1">
       <c r="A476" s="3">
         <v>2026</v>
       </c>
@@ -18087,7 +18121,7 @@
         <v>3.0306482852911016</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" hidden="1">
       <c r="A477" s="3">
         <v>2026</v>
       </c>
@@ -18124,7 +18158,7 @@
         <v>1.4723797337446647</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" hidden="1">
       <c r="A478" s="3">
         <v>2026</v>
       </c>
@@ -18161,7 +18195,7 @@
         <v>2.1419619459952148</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" hidden="1">
       <c r="A479" s="3">
         <v>2026</v>
       </c>
@@ -18198,7 +18232,7 @@
         <v>2.1875356044206451</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" hidden="1">
       <c r="A480" s="3">
         <v>2026</v>
       </c>
@@ -18235,7 +18269,7 @@
         <v>1.598583710922779</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" hidden="1">
       <c r="A481" s="3">
         <v>2026</v>
       </c>
@@ -18272,7 +18306,7 @@
         <v>3.5442283590853716</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" hidden="1">
       <c r="A482" s="3">
         <v>2026</v>
       </c>
@@ -18309,7 +18343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" hidden="1">
       <c r="A483" s="3">
         <v>2026</v>
       </c>
@@ -18346,7 +18380,7 @@
         <v>1.6113540564180222</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" hidden="1">
       <c r="A484" s="3">
         <v>2026</v>
       </c>
@@ -18383,7 +18417,7 @@
         <v>3.053435114503817</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" hidden="1">
       <c r="A485" s="3">
         <v>2026</v>
       </c>
@@ -18420,7 +18454,7 @@
         <v>1.4285589083355974</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" hidden="1">
       <c r="A486" s="3">
         <v>2026</v>
       </c>
@@ -18457,7 +18491,7 @@
         <v>1.0368007291785348</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" hidden="1">
       <c r="A487" s="3">
         <v>2026</v>
       </c>
@@ -18494,7 +18528,7 @@
         <v>1.0254073145721774</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" hidden="1">
       <c r="A488" s="3">
         <v>2026</v>
       </c>
@@ -18531,7 +18565,7 @@
         <v>1.6301347052173074</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" hidden="1">
       <c r="A489" s="3">
         <v>2026</v>
       </c>
@@ -18568,7 +18602,7 @@
         <v>2.5345965416604588</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" hidden="1">
       <c r="A490" s="3">
         <v>2026</v>
       </c>
@@ -18605,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" hidden="1">
       <c r="A491" s="3">
         <v>2026</v>
       </c>
@@ -18642,7 +18676,7 @@
         <v>2.4495836918273972</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" hidden="1">
       <c r="A492" s="3">
         <v>2026</v>
       </c>
@@ -18679,7 +18713,7 @@
         <v>6.220804375071209</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" hidden="1">
       <c r="A493" s="3">
         <v>2026</v>
       </c>
@@ -18716,7 +18750,7 @@
         <v>2.7607120007712465</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" hidden="1">
       <c r="A494" s="3">
         <v>2026</v>
       </c>
@@ -18753,7 +18787,7 @@
         <v>2.3926170673350806</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" hidden="1">
       <c r="A495" s="3">
         <v>2026</v>
       </c>
@@ -18790,7 +18824,7 @@
         <v>2.5065512133986556</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" hidden="1">
       <c r="A496" s="3">
         <v>2026</v>
       </c>
@@ -18827,7 +18861,7 @@
         <v>1.1568697907993795</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" hidden="1">
       <c r="A497" s="3">
         <v>2026</v>
       </c>
@@ -18864,7 +18898,7 @@
         <v>2.7975214941148629</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" hidden="1">
       <c r="A498" s="3">
         <v>2026</v>
       </c>
@@ -18901,7 +18935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" hidden="1">
       <c r="A499" s="3">
         <v>2026</v>
       </c>
@@ -18938,7 +18972,7 @@
         <v>1.4404528686161107</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" hidden="1">
       <c r="A500" s="3">
         <v>2026</v>
       </c>
@@ -18975,7 +19009,7 @@
         <v>3.8737609661615586</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" hidden="1">
       <c r="A501" s="3">
         <v>2026</v>
       </c>
@@ -19012,7 +19046,7 @@
         <v>1.5512572194809862</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" hidden="1">
       <c r="A502" s="3">
         <v>2026</v>
       </c>
@@ -19049,7 +19083,7 @@
         <v>1.8913068246553493</v>
       </c>
     </row>
-    <row r="503" spans="1:11">
+    <row r="503" spans="1:11" hidden="1">
       <c r="A503" s="3">
         <v>2026</v>
       </c>
@@ -19086,7 +19120,7 @@
         <v>1.8115529224108466</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" hidden="1">
       <c r="A504" s="3">
         <v>2026</v>
       </c>
@@ -19123,7 +19157,7 @@
         <v>2.4189095625805206</v>
       </c>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" hidden="1">
       <c r="A505" s="3">
         <v>2026</v>
       </c>
@@ -19160,7 +19194,7 @@
         <v>1.9877126405552974</v>
       </c>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" hidden="1">
       <c r="A506" s="3">
         <v>2026</v>
       </c>
@@ -19197,7 +19231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" spans="1:11" hidden="1">
       <c r="A507" s="3">
         <v>2026</v>
       </c>
@@ -19234,7 +19268,7 @@
         <v>1.5055580830168389</v>
       </c>
     </row>
-    <row r="508" spans="1:11">
+    <row r="508" spans="1:11" hidden="1">
       <c r="A508" s="3">
         <v>2026</v>
       </c>
@@ -19271,7 +19305,7 @@
         <v>5.0358892560100266</v>
       </c>
     </row>
-    <row r="509" spans="1:11">
+    <row r="509" spans="1:11" hidden="1">
       <c r="A509" s="3">
         <v>2026</v>
       </c>
@@ -19308,7 +19342,7 @@
         <v>1.6651913655445614</v>
       </c>
     </row>
-    <row r="510" spans="1:11">
+    <row r="510" spans="1:11" hidden="1">
       <c r="A510" s="3">
         <v>2026</v>
       </c>
@@ -19345,7 +19379,7 @@
         <v>1.4127834111883333</v>
       </c>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" hidden="1">
       <c r="A511" s="3">
         <v>2026</v>
       </c>
@@ -19382,7 +19416,7 @@
         <v>1.2988492651247578</v>
       </c>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" hidden="1">
       <c r="A512" s="3">
         <v>2026</v>
       </c>
@@ -19419,7 +19453,7 @@
         <v>2.6292495245440444</v>
       </c>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" spans="1:11" hidden="1">
       <c r="A513" s="3">
         <v>2026</v>
       </c>
@@ -19456,7 +19490,7 @@
         <v>1.9877126405552974</v>
       </c>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" spans="1:11" hidden="1">
       <c r="A514" s="3">
         <v>2026</v>
       </c>
@@ -19493,7 +19527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" hidden="1">
       <c r="A515" s="3">
         <v>2026</v>
       </c>
@@ -19530,7 +19564,7 @@
         <v>1.8148078514202977</v>
       </c>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" hidden="1">
       <c r="A516" s="3">
         <v>2026</v>
       </c>
@@ -19567,7 +19601,7 @@
         <v>7.9753902244502681</v>
       </c>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" hidden="1">
       <c r="A517" s="3">
         <v>2026</v>
       </c>
@@ -19604,7 +19638,7 @@
         <v>2.9973444579802102</v>
       </c>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" spans="1:11" hidden="1">
       <c r="A518" s="3">
         <v>2026</v>
       </c>
@@ -19641,7 +19675,7 @@
         <v>2.4951577987922979</v>
       </c>
     </row>
-    <row r="519" spans="1:11">
+    <row r="519" spans="1:11" hidden="1">
       <c r="A519" s="3">
         <v>2026</v>
       </c>
@@ -19678,7 +19712,7 @@
         <v>2.1989290190270023</v>
       </c>
     </row>
-    <row r="520" spans="1:11">
+    <row r="520" spans="1:11" hidden="1">
       <c r="A520" s="3">
         <v>2026</v>
       </c>
@@ -19715,7 +19749,7 @@
         <v>3.0499294484710915</v>
       </c>
     </row>
-    <row r="521" spans="1:11">
+    <row r="521" spans="1:11" hidden="1">
       <c r="A521" s="3">
         <v>2026</v>
       </c>
@@ -19752,7 +19786,7 @@
         <v>3.3549223933182004</v>
       </c>
     </row>
-    <row r="522" spans="1:11">
+    <row r="522" spans="1:11" hidden="1">
       <c r="A522" s="3">
         <v>2026</v>
       </c>
@@ -19789,7 +19823,7 @@
         <v>1.3265187434148373</v>
       </c>
     </row>
-    <row r="523" spans="1:11">
+    <row r="523" spans="1:11" hidden="1">
       <c r="A523" s="3">
         <v>2026</v>
       </c>
@@ -19826,7 +19860,7 @@
         <v>2.1472204450443035</v>
       </c>
     </row>
-    <row r="524" spans="1:11">
+    <row r="524" spans="1:11" hidden="1">
       <c r="A524" s="3">
         <v>2026</v>
       </c>
@@ -19863,7 +19897,7 @@
         <v>1.7353046861990697</v>
       </c>
     </row>
-    <row r="525" spans="1:11">
+    <row r="525" spans="1:11" hidden="1">
       <c r="A525" s="3">
         <v>2026</v>
       </c>
@@ -19900,7 +19934,7 @@
         <v>1.834339751623562</v>
       </c>
     </row>
-    <row r="526" spans="1:11">
+    <row r="526" spans="1:11" hidden="1">
       <c r="A526" s="3">
         <v>2026</v>
       </c>
@@ -19937,7 +19971,7 @@
         <v>1.6520451179218416</v>
       </c>
     </row>
-    <row r="527" spans="1:11">
+    <row r="527" spans="1:11" hidden="1">
       <c r="A527" s="3">
         <v>2026</v>
       </c>
@@ -19974,7 +20008,7 @@
         <v>1.8720256614753603</v>
       </c>
     </row>
-    <row r="528" spans="1:11">
+    <row r="528" spans="1:11" hidden="1">
       <c r="A528" s="3">
         <v>2026</v>
       </c>
@@ -20011,7 +20045,7 @@
         <v>2.4820115511695788</v>
       </c>
     </row>
-    <row r="529" spans="1:11">
+    <row r="529" spans="1:11" hidden="1">
       <c r="A529" s="3">
         <v>2026</v>
       </c>
@@ -20048,7 +20082,7 @@
         <v>2.1240576198237582</v>
       </c>
     </row>
-    <row r="530" spans="1:11">
+    <row r="530" spans="1:11" hidden="1">
       <c r="A530" s="3">
         <v>2026</v>
       </c>
@@ -20085,7 +20119,7 @@
         <v>3.3479110612527507</v>
       </c>
     </row>
-    <row r="531" spans="1:11">
+    <row r="531" spans="1:11" hidden="1">
       <c r="A531" s="3">
         <v>2026</v>
       </c>
@@ -20122,7 +20156,7 @@
         <v>4.0928650932068971</v>
       </c>
     </row>
-    <row r="532" spans="1:11">
+    <row r="532" spans="1:11" hidden="1">
       <c r="A532" s="3">
         <v>2026</v>
       </c>
@@ -20159,7 +20193,7 @@
         <v>2.4723709695795835</v>
       </c>
     </row>
-    <row r="533" spans="1:11">
+    <row r="533" spans="1:11" hidden="1">
       <c r="A533" s="3">
         <v>2026</v>
       </c>
@@ -20196,7 +20230,7 @@
         <v>2.1305685313888576</v>
       </c>
     </row>
-    <row r="534" spans="1:11">
+    <row r="534" spans="1:11" hidden="1">
       <c r="A534" s="3">
         <v>2026</v>
       </c>
@@ -20233,7 +20267,7 @@
         <v>2.2296035968133507</v>
       </c>
     </row>
-    <row r="535" spans="1:11">
+    <row r="535" spans="1:11" hidden="1">
       <c r="A535" s="3">
         <v>2026</v>
       </c>
@@ -20270,7 +20304,7 @@
         <v>4.0911122601905348</v>
       </c>
     </row>
-    <row r="536" spans="1:11">
+    <row r="536" spans="1:11" hidden="1">
       <c r="A536" s="3">
         <v>2026</v>
       </c>
@@ -20307,7 +20341,7 @@
         <v>2.7832479156311312</v>
       </c>
     </row>
-    <row r="537" spans="1:11">
+    <row r="537" spans="1:11" hidden="1">
       <c r="A537" s="3">
         <v>2026</v>
       </c>
@@ -20344,7 +20378,7 @@
         <v>3.3040902358436832</v>
       </c>
     </row>
-    <row r="538" spans="1:11">
+    <row r="538" spans="1:11" hidden="1">
       <c r="A538" s="3">
         <v>2026</v>
       </c>
@@ -20381,7 +20415,7 @@
         <v>3.7773551502616116</v>
       </c>
     </row>
-    <row r="539" spans="1:11">
+    <row r="539" spans="1:11" hidden="1">
       <c r="A539" s="3">
         <v>2026</v>
       </c>
@@ -20418,7 +20452,7 @@
         <v>4.2041699897459281</v>
       </c>
     </row>
-    <row r="540" spans="1:11">
+    <row r="540" spans="1:11" hidden="1">
       <c r="A540" s="3">
         <v>2026</v>
       </c>
@@ -20455,7 +20489,7 @@
         <v>3.5433519425771913</v>
       </c>
     </row>
-    <row r="541" spans="1:11">
+    <row r="541" spans="1:11" hidden="1">
       <c r="A541" s="3">
         <v>2026</v>
       </c>
@@ -20492,7 +20526,7 @@
         <v>3.4495753762017878</v>
       </c>
     </row>
-    <row r="542" spans="1:11">
+    <row r="542" spans="1:11" hidden="1">
       <c r="A542" s="3">
         <v>2026</v>
       </c>
@@ -20529,7 +20563,7 @@
         <v>6.1839948817275951</v>
       </c>
     </row>
-    <row r="543" spans="1:11">
+    <row r="543" spans="1:11" hidden="1">
       <c r="A543" s="3">
         <v>2026</v>
       </c>
@@ -20566,7 +20600,7 @@
         <v>3.9551417748442388</v>
       </c>
     </row>
-    <row r="544" spans="1:11">
+    <row r="544" spans="1:11" hidden="1">
       <c r="A544" s="3">
         <v>2026</v>
       </c>
@@ -20603,7 +20637,7 @@
         <v>2.0332862989807281</v>
       </c>
     </row>
-    <row r="545" spans="1:11">
+    <row r="545" spans="1:11" hidden="1">
       <c r="A545" s="3">
         <v>2026</v>
       </c>
@@ -20640,7 +20674,7 @@
         <v>2.7607120007712473</v>
       </c>
     </row>
-    <row r="546" spans="1:11">
+    <row r="546" spans="1:11" hidden="1">
       <c r="A546" s="3">
         <v>2026</v>
       </c>
@@ -20677,7 +20711,7 @@
         <v>5.1612168166799597</v>
       </c>
     </row>
-    <row r="547" spans="1:11">
+    <row r="547" spans="1:11" hidden="1">
       <c r="A547" s="3">
         <v>2026</v>
       </c>
@@ -20714,7 +20748,7 @@
         <v>4.4662185256921507</v>
       </c>
     </row>
-    <row r="548" spans="1:11">
+    <row r="548" spans="1:11" hidden="1">
       <c r="A548" s="3">
         <v>2026</v>
       </c>
@@ -20751,7 +20785,7 @@
         <v>4.4171392012339963</v>
       </c>
     </row>
-    <row r="549" spans="1:11">
+    <row r="549" spans="1:11" hidden="1">
       <c r="A549" s="3">
         <v>2026</v>
       </c>
@@ -20788,7 +20822,7 @@
         <v>6.1103758950403613</v>
       </c>
     </row>
-    <row r="550" spans="1:11">
+    <row r="550" spans="1:11" hidden="1">
       <c r="A550" s="3">
         <v>2026</v>
       </c>
@@ -20825,7 +20859,7 @@
         <v>3.1576028984353162</v>
       </c>
     </row>
-    <row r="551" spans="1:11">
+    <row r="551" spans="1:11" hidden="1">
       <c r="A551" s="3">
         <v>2026</v>
       </c>
@@ -20862,7 +20896,7 @@
         <v>1.7177763560354422</v>
       </c>
     </row>
-    <row r="552" spans="1:11">
+    <row r="552" spans="1:11" hidden="1">
       <c r="A552" s="3">
         <v>2026</v>
       </c>
@@ -20899,7 +20933,7 @@
         <v>2.4802587181532152</v>
       </c>
     </row>
-    <row r="553" spans="1:11">
+    <row r="553" spans="1:11" hidden="1">
       <c r="A553" s="3">
         <v>2026</v>
       </c>
@@ -20936,7 +20970,7 @@
         <v>3.2471231628118948</v>
       </c>
     </row>
-    <row r="554" spans="1:11">
+    <row r="554" spans="1:11" hidden="1">
       <c r="A554" s="3">
         <v>2026</v>
       </c>
@@ -20973,7 +21007,7 @@
         <v>2.9850746268656718</v>
       </c>
     </row>
-    <row r="555" spans="1:11">
+    <row r="555" spans="1:11" hidden="1">
       <c r="A555" s="3">
         <v>2026</v>
       </c>
@@ -21010,7 +21044,7 @@
         <v>2.9552764655875059</v>
       </c>
     </row>
-    <row r="556" spans="1:11">
+    <row r="556" spans="1:11" hidden="1">
       <c r="A556" s="3">
         <v>2026</v>
       </c>
@@ -21047,7 +21081,7 @@
         <v>4.3224862183504085</v>
       </c>
     </row>
-    <row r="557" spans="1:11">
+    <row r="557" spans="1:11" hidden="1">
       <c r="A557" s="3">
         <v>2026</v>
       </c>
@@ -21084,7 +21118,7 @@
         <v>1.7578407888196605</v>
       </c>
     </row>
-    <row r="558" spans="1:11">
+    <row r="558" spans="1:11" hidden="1">
       <c r="A558" s="3">
         <v>2026</v>
       </c>
@@ -21121,7 +21155,7 @@
         <v>1.1042848003084986</v>
       </c>
     </row>
-    <row r="559" spans="1:11">
+    <row r="559" spans="1:11" hidden="1">
       <c r="A559" s="3">
         <v>2026</v>
       </c>
@@ -21158,7 +21192,7 @@
         <v>1.4723797337446647</v>
       </c>
     </row>
-    <row r="560" spans="1:11">
+    <row r="560" spans="1:11" hidden="1">
       <c r="A560" s="3">
         <v>2026</v>
       </c>
@@ -21195,7 +21229,7 @@
         <v>2.5407314572177282</v>
       </c>
     </row>
-    <row r="561" spans="1:11">
+    <row r="561" spans="1:11" hidden="1">
       <c r="A561" s="3">
         <v>2026</v>
       </c>
@@ -21232,7 +21266,7 @@
         <v>3.0192548706847444</v>
       </c>
     </row>
-    <row r="562" spans="1:11">
+    <row r="562" spans="1:11" hidden="1">
       <c r="A562" s="3">
         <v>2026</v>
       </c>
@@ -21269,7 +21303,7 @@
         <v>1.7773726785917738</v>
       </c>
     </row>
-    <row r="563" spans="1:11">
+    <row r="563" spans="1:11" hidden="1">
       <c r="A563" s="3">
         <v>2026</v>
       </c>
@@ -21306,7 +21340,7 @@
         <v>2.7764874979185108</v>
       </c>
     </row>
-    <row r="564" spans="1:11">
+    <row r="564" spans="1:11" hidden="1">
       <c r="A564" s="3">
         <v>2026</v>
       </c>
@@ -21343,7 +21377,7 @@
         <v>1.961294583821936</v>
       </c>
     </row>
-    <row r="565" spans="1:11">
+    <row r="565" spans="1:11" hidden="1">
       <c r="A565" s="3">
         <v>2026</v>
       </c>
@@ -21380,7 +21414,7 @@
         <v>1.0779923050630582</v>
       </c>
     </row>
-    <row r="566" spans="1:11">
+    <row r="566" spans="1:11" hidden="1">
       <c r="A566" s="3">
         <v>2026</v>
       </c>
@@ -21417,7 +21451,7 @@
         <v>1.4460872384992243</v>
       </c>
     </row>
-    <row r="567" spans="1:11">
+    <row r="567" spans="1:11" hidden="1">
       <c r="A567" s="3">
         <v>2026</v>
       </c>
@@ -21454,7 +21488,7 @@
         <v>1.6862253617409138</v>
       </c>
     </row>
-    <row r="568" spans="1:11">
+    <row r="568" spans="1:11" hidden="1">
       <c r="A568" s="3">
         <v>2026</v>
       </c>
@@ -21491,7 +21525,7 @@
         <v>1.9027002392617067</v>
       </c>
     </row>
-    <row r="569" spans="1:11">
+    <row r="569" spans="1:11" hidden="1">
       <c r="A569" s="3">
         <v>2026</v>
       </c>
@@ -21528,7 +21562,7 @@
         <v>2.1033996196352356</v>
       </c>
     </row>
-    <row r="570" spans="1:11">
+    <row r="570" spans="1:11" hidden="1">
       <c r="A570" s="3">
         <v>2026</v>
       </c>
@@ -21565,7 +21599,7 @@
         <v>2.3347735777951111</v>
       </c>
     </row>
-    <row r="571" spans="1:11">
+    <row r="571" spans="1:11" hidden="1">
       <c r="A571" s="3">
         <v>2026</v>
       </c>
@@ -21602,7 +21636,7 @@
         <v>1.6439066636183861</v>
       </c>
     </row>
-    <row r="572" spans="1:11">
+    <row r="572" spans="1:11" hidden="1">
       <c r="A572" s="3">
         <v>2026</v>
       </c>
@@ -21639,7 +21673,7 @@
         <v>2.0332862989807277</v>
       </c>
     </row>
-    <row r="573" spans="1:11">
+    <row r="573" spans="1:11" hidden="1">
       <c r="A573" s="3">
         <v>2026</v>
       </c>
@@ -21676,7 +21710,7 @@
         <v>2.3137395815987589</v>
       </c>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" hidden="1">
       <c r="A574" s="3">
         <v>2026</v>
       </c>
@@ -21713,7 +21747,7 @@
         <v>2.1419619459952148</v>
       </c>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" hidden="1">
       <c r="A575" s="3">
         <v>2026</v>
       </c>
@@ -21750,7 +21784,7 @@
         <v>2.4381907257605104</v>
       </c>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" hidden="1">
       <c r="A576" s="3">
         <v>2026</v>
       </c>
@@ -21787,7 +21821,7 @@
         <v>2.2611545911078781</v>
       </c>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:12" hidden="1">
       <c r="A577" s="3">
         <v>2026</v>
       </c>
@@ -21824,7 +21858,7 @@
         <v>2.1980526025188212</v>
       </c>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:12" hidden="1">
       <c r="A578" s="3">
         <v>2026</v>
       </c>
@@ -21861,7 +21895,7 @@
         <v>0.43864646234476468</v>
       </c>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:12" hidden="1">
       <c r="A579" s="3">
         <v>2026</v>
       </c>
@@ -21898,7 +21932,7 @@
         <v>1.7171500298192053</v>
       </c>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:12" hidden="1">
       <c r="A580" s="3">
         <v>2026</v>
       </c>
@@ -21935,7 +21969,7 @@
         <v>4.4297595989518062</v>
       </c>
     </row>
-    <row r="581" spans="1:11">
+    <row r="581" spans="1:12" hidden="1">
       <c r="A581" s="3">
         <v>2026</v>
       </c>
@@ -21972,7 +22006,7 @@
         <v>1.9351276500644166</v>
       </c>
     </row>
-    <row r="582" spans="1:11">
+    <row r="582" spans="1:12" hidden="1">
       <c r="A582" s="3">
         <v>2026</v>
       </c>
@@ -22009,7 +22043,7 @@
         <v>1.4127834111883333</v>
       </c>
     </row>
-    <row r="583" spans="1:11">
+    <row r="583" spans="1:12" hidden="1">
       <c r="A583" s="3">
         <v>2026</v>
       </c>
@@ -22046,7 +22080,7 @@
         <v>1.6178648741027686</v>
       </c>
     </row>
-    <row r="584" spans="1:11">
+    <row r="584" spans="1:12" hidden="1">
       <c r="A584" s="3">
         <v>2026</v>
       </c>
@@ -22083,7 +22117,7 @@
         <v>2.4714945530714014</v>
       </c>
     </row>
-    <row r="585" spans="1:11">
+    <row r="585" spans="1:12" hidden="1">
       <c r="A585" s="3">
         <v>2026</v>
       </c>
@@ -22120,7 +22154,7 @@
         <v>1.609100709020955</v>
       </c>
     </row>
-    <row r="586" spans="1:11">
+    <row r="586" spans="1:12">
       <c r="A586" s="3">
         <v>2026</v>
       </c>
@@ -22157,7 +22191,7 @@
         <v>0.43864646234476468</v>
       </c>
     </row>
-    <row r="587" spans="1:11">
+    <row r="587" spans="1:12">
       <c r="A587" s="3">
         <v>2026</v>
       </c>
@@ -22193,8 +22227,11 @@
         <f t="shared" si="18"/>
         <v>1.8310841550204797</v>
       </c>
-    </row>
-    <row r="588" spans="1:11">
+      <c r="L587" s="11">
+        <v>5611</v>
+      </c>
+    </row>
+    <row r="588" spans="1:12">
       <c r="A588" s="3">
         <v>2026</v>
       </c>
@@ -22230,8 +22267,11 @@
         <f t="shared" si="18"/>
         <v>4.3568417454711179</v>
       </c>
-    </row>
-    <row r="589" spans="1:11">
+      <c r="L588" s="11">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="589" spans="1:12">
       <c r="A589" s="3">
         <v>2026</v>
       </c>
@@ -22267,8 +22307,11 @@
         <f t="shared" si="18"/>
         <v>1.8299576690826549</v>
       </c>
-    </row>
-    <row r="590" spans="1:11">
+      <c r="L589" s="11">
+        <v>5774</v>
+      </c>
+    </row>
+    <row r="590" spans="1:12">
       <c r="A590" s="3">
         <v>2026</v>
       </c>
@@ -22304,8 +22347,11 @@
         <f t="shared" si="18"/>
         <v>1.2988492651247578</v>
       </c>
-    </row>
-    <row r="591" spans="1:11">
+      <c r="L590" s="12">
+        <v>4729</v>
+      </c>
+    </row>
+    <row r="591" spans="1:12">
       <c r="A591" s="3">
         <v>2026</v>
       </c>
@@ -22341,8 +22387,11 @@
         <f t="shared" si="18"/>
         <v>1.6520451179218412</v>
       </c>
-    </row>
-    <row r="592" spans="1:11">
+      <c r="L591" s="12">
+        <v>5153</v>
+      </c>
+    </row>
+    <row r="592" spans="1:12">
       <c r="A592" s="3">
         <v>2026</v>
       </c>
@@ -22378,8 +22427,11 @@
         <f t="shared" si="18"/>
         <v>1.2725567698793174</v>
       </c>
-    </row>
-    <row r="593" spans="1:11">
+      <c r="L592" s="12">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="593" spans="1:12">
       <c r="A593" s="3">
         <v>2026</v>
       </c>
@@ -22415,8 +22467,11 @@
         <f t="shared" si="18"/>
         <v>1.3146247622720222</v>
       </c>
-    </row>
-    <row r="594" spans="1:11">
+      <c r="L593" s="12">
+        <v>6234</v>
+      </c>
+    </row>
+    <row r="594" spans="1:12">
       <c r="A594" s="3">
         <v>2026</v>
       </c>
@@ -22453,7 +22508,7 @@
         <v>0.31331890167483195</v>
       </c>
     </row>
-    <row r="595" spans="1:11">
+    <row r="595" spans="1:12">
       <c r="A595" s="3">
         <v>2026</v>
       </c>
@@ -22489,8 +22544,11 @@
         <f t="shared" si="18"/>
         <v>1.4485910204162016</v>
       </c>
-    </row>
-    <row r="596" spans="1:11">
+      <c r="L595" s="11">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="596" spans="1:12">
       <c r="A596" s="3">
         <v>2026</v>
       </c>
@@ -22526,8 +22584,11 @@
         <f t="shared" si="18"/>
         <v>2.8984846758573544</v>
       </c>
-    </row>
-    <row r="597" spans="1:11">
+      <c r="L596" s="11">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="597" spans="1:12">
       <c r="A597" s="3">
         <v>2026</v>
       </c>
@@ -22563,8 +22624,11 @@
         <f t="shared" si="18"/>
         <v>1.2970964321083951</v>
       </c>
-    </row>
-    <row r="598" spans="1:11">
+      <c r="L597" s="11">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="598" spans="1:12">
       <c r="A598" s="3">
         <v>2026</v>
       </c>
@@ -22600,8 +22664,11 @@
         <f t="shared" si="18"/>
         <v>0.91147316850860205</v>
       </c>
-    </row>
-    <row r="599" spans="1:11">
+      <c r="L598" s="12">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="599" spans="1:12">
       <c r="A599" s="3">
         <v>2026</v>
       </c>
@@ -22637,8 +22704,11 @@
         <f t="shared" si="18"/>
         <v>1.2418821920929703</v>
       </c>
-    </row>
-    <row r="600" spans="1:11">
+      <c r="L599" s="12">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="600" spans="1:12">
       <c r="A600" s="3">
         <v>2026</v>
       </c>
@@ -22674,8 +22744,11 @@
         <f t="shared" si="18"/>
         <v>1.241005775584789</v>
       </c>
-    </row>
-    <row r="601" spans="1:11">
+      <c r="L600" s="12">
+        <v>4468</v>
+      </c>
+    </row>
+    <row r="601" spans="1:12">
       <c r="A601" s="3">
         <v>2026</v>
       </c>
@@ -22711,8 +22784,11 @@
         <f t="shared" si="18"/>
         <v>1.2199717793884366</v>
       </c>
-    </row>
-    <row r="602" spans="1:11">
+      <c r="L601" s="12">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="602" spans="1:12">
       <c r="A602" s="3">
         <v>2026</v>
       </c>
@@ -22749,7 +22825,7 @@
         <v>0.39876951122251336</v>
       </c>
     </row>
-    <row r="603" spans="1:11">
+    <row r="603" spans="1:12">
       <c r="A603" s="3">
         <v>2026</v>
       </c>
@@ -22785,8 +22861,11 @@
         <f t="shared" si="18"/>
         <v>1.5543869938173849</v>
       </c>
-    </row>
-    <row r="604" spans="1:11">
+      <c r="L603" s="11">
+        <v>3802</v>
+      </c>
+    </row>
+    <row r="604" spans="1:12">
       <c r="A604" s="3">
         <v>2026</v>
       </c>
@@ -22822,8 +22901,11 @@
         <f t="shared" si="18"/>
         <v>2.7708784322661502</v>
       </c>
-    </row>
-    <row r="605" spans="1:11">
+      <c r="L604" s="11">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="605" spans="1:12">
       <c r="A605" s="3">
         <v>2026</v>
       </c>
@@ -22859,8 +22941,11 @@
         <f t="shared" si="18"/>
         <v>1.1288244625375763</v>
       </c>
-    </row>
-    <row r="606" spans="1:11">
+      <c r="L605" s="11">
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="606" spans="1:12">
       <c r="A606" s="3">
         <v>2026</v>
       </c>
@@ -22896,8 +22981,11 @@
         <f t="shared" si="18"/>
         <v>0.92286658311495962</v>
       </c>
-    </row>
-    <row r="607" spans="1:11">
+      <c r="L606" s="12">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="607" spans="1:12">
       <c r="A607" s="3">
         <v>2026</v>
       </c>
@@ -22933,8 +23021,11 @@
         <f t="shared" si="18"/>
         <v>1.0937678022103225</v>
       </c>
-    </row>
-    <row r="608" spans="1:11">
+      <c r="L607" s="12">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="608" spans="1:12">
       <c r="A608" s="3">
         <v>2026</v>
       </c>
@@ -22970,8 +23061,11 @@
         <f t="shared" si="18"/>
         <v>1.0201488155230891</v>
       </c>
-    </row>
-    <row r="609" spans="1:11">
+      <c r="L608" s="12">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="609" spans="1:12">
       <c r="A609" s="3">
         <v>2026</v>
       </c>
@@ -23007,8 +23101,11 @@
         <f t="shared" si="18"/>
         <v>0.82032585165774174</v>
       </c>
-    </row>
-    <row r="610" spans="1:11">
+      <c r="L609" s="12">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="610" spans="1:12">
       <c r="A610" s="3">
         <v>2026</v>
       </c>
@@ -23045,7 +23142,7 @@
         <v>0.42155634043522844</v>
       </c>
     </row>
-    <row r="611" spans="1:11">
+    <row r="611" spans="1:12">
       <c r="A611" s="3">
         <v>2026</v>
       </c>
@@ -23081,8 +23178,11 @@
         <f t="shared" si="18"/>
         <v>1.4404528686161107</v>
       </c>
-    </row>
-    <row r="612" spans="1:11">
+      <c r="L611" s="11">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="612" spans="1:12">
       <c r="A612" s="3">
         <v>2026</v>
       </c>
@@ -23118,8 +23218,11 @@
         <f t="shared" si="18"/>
         <v>3.9421214537997038</v>
       </c>
-    </row>
-    <row r="613" spans="1:11">
+      <c r="L612" s="11">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="613" spans="1:12">
       <c r="A613" s="3">
         <v>2026</v>
       </c>
@@ -23155,8 +23258,11 @@
         <f t="shared" si="18"/>
         <v>1.6827196957081882</v>
       </c>
-    </row>
-    <row r="614" spans="1:11">
+      <c r="L613" s="11">
+        <v>4766</v>
+      </c>
+    </row>
+    <row r="614" spans="1:12">
       <c r="A614" s="3">
         <v>2026</v>
       </c>
@@ -23192,8 +23298,11 @@
         <f t="shared" si="18"/>
         <v>0.85450609547681444</v>
       </c>
-    </row>
-    <row r="615" spans="1:11">
+      <c r="L614" s="12">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="615" spans="1:12">
       <c r="A615" s="3">
         <v>2026</v>
       </c>
@@ -23229,8 +23338,11 @@
         <f t="shared" si="18"/>
         <v>1.0254073145721774</v>
       </c>
-    </row>
-    <row r="616" spans="1:11">
+      <c r="L615" s="12">
+        <v>3697</v>
+      </c>
+    </row>
+    <row r="616" spans="1:12">
       <c r="A616" s="3">
         <v>2026</v>
       </c>
@@ -23266,8 +23378,11 @@
         <f t="shared" si="18"/>
         <v>0.93601283073767971</v>
       </c>
-    </row>
-    <row r="617" spans="1:11">
+      <c r="L616" s="12">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="617" spans="1:12">
       <c r="A617" s="3">
         <v>2026</v>
       </c>
@@ -23303,11 +23418,25 @@
         <f t="shared" si="18"/>
         <v>1.1989377831920842</v>
       </c>
+      <c r="L617" s="12">
+        <v>5774</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K609">
-    <filterColumn colId="0"/>
-    <filterColumn colId="1"/>
+  <autoFilter ref="A1:K617">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2026"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="23"/>
+        <filter val="24"/>
+        <filter val="25"/>
+        <filter val="26"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5"/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
